--- a/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="1 Board" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="263">
   <si>
     <t>Component list</t>
   </si>
@@ -795,16 +795,33 @@
   </si>
   <si>
     <t>Quantity Per Board</t>
+  </si>
+  <si>
+    <t>Total Cost(5 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Total Cost (2 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (1 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,6 +967,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -977,7 +1001,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1167,11 +1191,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1350,6 +1398,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,13 +1457,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1431,13 +1511,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1485,13 +1565,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1799,7 +1879,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="22" customWidth="1"/>
@@ -1811,1863 +1891,8 @@
     <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="66"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="67"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="67"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="67"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="67"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="39">
-        <f>ROW(B10) - ROW($B$9)</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="J10" s="27">
-        <v>4</v>
-      </c>
-      <c r="K10" s="27"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="41">
-        <f t="shared" ref="B11:B61" si="0">ROW(B11) - ROW($B$9)</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="J11" s="28">
-        <v>4</v>
-      </c>
-      <c r="K11" s="28"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="39">
-        <f>ROW(B12) - ROW($B$9)</f>
-        <v>3</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="J12" s="27">
-        <v>1</v>
-      </c>
-      <c r="K12" s="27"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="41">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="J13" s="28">
-        <v>1</v>
-      </c>
-      <c r="K13" s="28"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="39">
-        <f>ROW(B14) - ROW($B$9)</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I14" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="J14" s="27">
-        <v>1</v>
-      </c>
-      <c r="K14" s="27"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="41">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="J15" s="28">
-        <v>2</v>
-      </c>
-      <c r="K15" s="28"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="39">
-        <f>ROW(B16) - ROW($B$9)</f>
-        <v>7</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="J16" s="27">
-        <v>1</v>
-      </c>
-      <c r="K16" s="27"/>
-    </row>
-    <row r="17" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="41">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="J17" s="28">
-        <v>1</v>
-      </c>
-      <c r="K17" s="28"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="39">
-        <f>ROW(B18) - ROW($B$9)</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="J18" s="27">
-        <v>1</v>
-      </c>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="19" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="41">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="J19" s="28">
-        <v>2</v>
-      </c>
-      <c r="K19" s="28"/>
-    </row>
-    <row r="20" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="39">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="I20" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="J20" s="27">
-        <v>1</v>
-      </c>
-      <c r="K20" s="27"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="41">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="J21" s="28">
-        <v>1</v>
-      </c>
-      <c r="K21" s="28"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="39">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="J22" s="27">
-        <v>1</v>
-      </c>
-      <c r="K22" s="27"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="41">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="J23" s="28">
-        <v>1</v>
-      </c>
-      <c r="K23" s="28"/>
-    </row>
-    <row r="24" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="39">
-        <f>ROW(B24) - ROW($B$9)</f>
-        <v>15</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="J24" s="27">
-        <v>1</v>
-      </c>
-      <c r="K24" s="27"/>
-    </row>
-    <row r="25" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="41">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="J25" s="28">
-        <v>1</v>
-      </c>
-      <c r="K25" s="28"/>
-    </row>
-    <row r="26" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="39">
-        <f>ROW(B26) - ROW($B$9)</f>
-        <v>17</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="J26" s="27">
-        <v>1</v>
-      </c>
-      <c r="K26" s="27"/>
-    </row>
-    <row r="27" spans="1:11" ht="36" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="41">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="J27" s="28">
-        <v>2</v>
-      </c>
-      <c r="K27" s="28"/>
-    </row>
-    <row r="28" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="39">
-        <f>ROW(B28) - ROW($B$9)</f>
-        <v>19</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="H28" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I28" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="J28" s="27">
-        <v>13</v>
-      </c>
-      <c r="K28" s="27"/>
-    </row>
-    <row r="29" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="41">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>251</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="J29" s="28">
-        <v>1</v>
-      </c>
-      <c r="K29" s="28"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="39">
-        <f>ROW(B30) - ROW($B$9)</f>
-        <v>21</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I30" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="J30" s="27">
-        <v>4</v>
-      </c>
-      <c r="K30" s="27"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="41">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="J31" s="28">
-        <v>2</v>
-      </c>
-      <c r="K31" s="28"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="39">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="J32" s="27">
-        <v>1</v>
-      </c>
-      <c r="K32" s="27"/>
-    </row>
-    <row r="33" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="39">
-        <f>ROW(B33) - ROW($B$9)</f>
-        <v>24</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="48" t="s">
-        <v>252</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="J33" s="28">
-        <v>1</v>
-      </c>
-      <c r="K33" s="28"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="41">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="J34" s="28">
-        <v>2</v>
-      </c>
-      <c r="K34" s="27"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="39">
-        <f>ROW(B35) - ROW($B$9)</f>
-        <v>26</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="H35" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I35" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="J35" s="27">
-        <v>1</v>
-      </c>
-      <c r="K35" s="28"/>
-    </row>
-    <row r="36" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="41">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I36" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="J36" s="28">
-        <v>2</v>
-      </c>
-      <c r="K36" s="27"/>
-    </row>
-    <row r="37" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="39">
-        <f>ROW(B37) - ROW($B$9)</f>
-        <v>28</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="H37" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="I37" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="J37" s="27">
-        <v>3</v>
-      </c>
-      <c r="K37" s="28"/>
-    </row>
-    <row r="38" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="41">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="J38" s="28">
-        <v>2</v>
-      </c>
-      <c r="K38" s="27"/>
-    </row>
-    <row r="39" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="39">
-        <f>ROW(B39) - ROW($B$9)</f>
-        <v>30</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="J39" s="27">
-        <v>3</v>
-      </c>
-      <c r="K39" s="28"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="41">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="J40" s="28">
-        <v>2</v>
-      </c>
-      <c r="K40" s="27"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="39">
-        <f>ROW(B41) - ROW($B$9)</f>
-        <v>32</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G41" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="H41" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I41" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="J41" s="27">
-        <v>3</v>
-      </c>
-      <c r="K41" s="28"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="41">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I42" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="J42" s="28">
-        <v>3</v>
-      </c>
-      <c r="K42" s="27"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="39">
-        <f>ROW(B43) - ROW($B$9)</f>
-        <v>34</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G43" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="J43" s="27">
-        <v>2</v>
-      </c>
-      <c r="K43" s="28"/>
-    </row>
-    <row r="44" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="41">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="H44" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I44" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="J44" s="28">
-        <v>3</v>
-      </c>
-      <c r="K44" s="27"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="39">
-        <f>ROW(B45) - ROW($B$9)</f>
-        <v>36</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G45" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="H45" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I45" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="J45" s="27">
-        <v>2</v>
-      </c>
-      <c r="K45" s="28"/>
-    </row>
-    <row r="46" spans="1:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="41">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="H46" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I46" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="J46" s="28">
-        <v>3</v>
-      </c>
-      <c r="K46" s="27"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="39">
-        <f>ROW(B47) - ROW($B$9)</f>
-        <v>38</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F47" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G47" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="H47" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I47" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="J47" s="27">
-        <v>2</v>
-      </c>
-      <c r="K47" s="28"/>
-    </row>
-    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="41">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="H48" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I48" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="J48" s="28">
-        <v>2</v>
-      </c>
-      <c r="K48" s="27"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="39">
-        <f>ROW(B49) - ROW($B$9)</f>
-        <v>40</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G49" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="H49" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I49" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="J49" s="27">
-        <v>3</v>
-      </c>
-      <c r="K49" s="28"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="41">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="H50" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I50" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="J50" s="28">
-        <v>1</v>
-      </c>
-      <c r="K50" s="27"/>
-    </row>
-    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="39">
-        <f>ROW(B51) - ROW($B$9)</f>
-        <v>42</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="F51" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="G51" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="H51" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="I51" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="J51" s="27">
-        <v>1</v>
-      </c>
-      <c r="K51" s="28"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="41">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="F52" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="H52" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="I52" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="J52" s="28">
-        <v>1</v>
-      </c>
-      <c r="K52" s="27"/>
-    </row>
-    <row r="53" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="39">
-        <f>ROW(B53) - ROW($B$9)</f>
-        <v>44</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="F53" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G53" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="H53" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="I53" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="J53" s="27">
-        <v>1</v>
-      </c>
-      <c r="K53" s="28"/>
-    </row>
-    <row r="54" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="41">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="F54" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="G54" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="H54" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I54" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="J54" s="28">
-        <v>1</v>
-      </c>
-      <c r="K54" s="27"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="39">
-        <f>ROW(B55) - ROW($B$9)</f>
-        <v>46</v>
-      </c>
-      <c r="C55" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="F55" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G55" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="H55" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I55" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="J55" s="27">
-        <v>1</v>
-      </c>
-      <c r="K55" s="28"/>
-    </row>
-    <row r="56" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="41">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="F56" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="G56" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="H56" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="I56" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="J56" s="28">
-        <v>1</v>
-      </c>
-      <c r="K56" s="27"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="41">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="H57" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I57" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="J57" s="28">
-        <v>1</v>
-      </c>
-      <c r="K57" s="28"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="39">
-        <f>ROW(B58) - ROW($B$9)</f>
-        <v>49</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="F58" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G58" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="H58" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="I58" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="J58" s="27">
-        <v>2</v>
-      </c>
-      <c r="K58" s="27"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="41">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="F59" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="G59" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="I59" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="J59" s="43">
-        <v>2</v>
-      </c>
-      <c r="K59" s="27"/>
-    </row>
-    <row r="60" spans="1:11" ht="48" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="39">
-        <f>ROW(B60) - ROW($B$9)</f>
-        <v>51</v>
-      </c>
-      <c r="C60" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E60" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="F60" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="G60" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="H60" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="I60" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="J60" s="27">
-        <v>9</v>
-      </c>
-      <c r="K60" s="27"/>
-    </row>
-    <row r="61" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="49">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="C61" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="D61" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E61" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="H61" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="I61" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="J61" s="51">
-        <v>3</v>
-      </c>
-      <c r="K61" s="27"/>
-    </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="52"/>
-      <c r="C62" s="53"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="56"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="K3:K8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="28.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3825,17 +2050,17 @@
         <v>239</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="L9" s="26" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
       <c r="B10" s="39">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -3864,14 +2089,13 @@
       <c r="J10" s="27">
         <v>4</v>
       </c>
-      <c r="K10" s="27">
-        <f>J10*2</f>
-        <v>8</v>
+      <c r="K10" s="68">
+        <v>1.2999999999999998</v>
       </c>
       <c r="L10" s="27"/>
     </row>
-    <row r="11" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B61" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -3900,14 +2124,13 @@
       <c r="J11" s="28">
         <v>4</v>
       </c>
-      <c r="K11" s="27">
-        <f t="shared" ref="K11:K61" si="1">J11*2</f>
-        <v>8</v>
+      <c r="K11" s="69">
+        <v>1.278</v>
       </c>
       <c r="L11" s="28"/>
     </row>
-    <row r="12" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
       <c r="B12" s="39">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -3936,14 +2159,13 @@
       <c r="J12" s="27">
         <v>1</v>
       </c>
-      <c r="K12" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K12" s="68">
+        <v>1.125</v>
       </c>
       <c r="L12" s="27"/>
     </row>
-    <row r="13" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="B13" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3972,14 +2194,13 @@
       <c r="J13" s="28">
         <v>1</v>
       </c>
-      <c r="K13" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K13" s="69">
+        <v>1</v>
       </c>
       <c r="L13" s="28"/>
     </row>
-    <row r="14" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
       <c r="B14" s="39">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -4008,14 +2229,13 @@
       <c r="J14" s="27">
         <v>1</v>
       </c>
-      <c r="K14" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K14" s="68">
+        <v>1.1339999999999999</v>
       </c>
       <c r="L14" s="27"/>
     </row>
-    <row r="15" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
       <c r="B15" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4044,14 +2264,13 @@
       <c r="J15" s="28">
         <v>2</v>
       </c>
-      <c r="K15" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K15" s="69">
+        <v>1.258</v>
       </c>
       <c r="L15" s="28"/>
     </row>
-    <row r="16" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
       <c r="B16" s="39">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -4080,14 +2299,13 @@
       <c r="J16" s="27">
         <v>1</v>
       </c>
-      <c r="K16" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K16" s="68">
+        <v>1.1499999999999999</v>
       </c>
       <c r="L16" s="27"/>
     </row>
-    <row r="17" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+    <row r="17" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
       <c r="B17" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -4116,14 +2334,13 @@
       <c r="J17" s="28">
         <v>1</v>
       </c>
-      <c r="K17" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K17" s="69">
+        <v>1.1599999999999999</v>
       </c>
       <c r="L17" s="28"/>
     </row>
-    <row r="18" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
       <c r="B18" s="39">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -4152,14 +2369,13 @@
       <c r="J18" s="27">
         <v>1</v>
       </c>
-      <c r="K18" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K18" s="68">
+        <v>1.08</v>
       </c>
       <c r="L18" s="27"/>
     </row>
-    <row r="19" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
+    <row r="19" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
       <c r="B19" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -4188,14 +2404,13 @@
       <c r="J19" s="28">
         <v>2</v>
       </c>
-      <c r="K19" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K19" s="69">
+        <v>1.9411</v>
       </c>
       <c r="L19" s="28"/>
     </row>
-    <row r="20" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
+    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
       <c r="B20" s="39">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -4224,14 +2439,13 @@
       <c r="J20" s="27">
         <v>1</v>
       </c>
-      <c r="K20" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K20" s="68">
+        <v>1.345</v>
       </c>
       <c r="L20" s="27"/>
     </row>
-    <row r="21" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
       <c r="B21" s="41">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4260,14 +2474,13 @@
       <c r="J21" s="28">
         <v>1</v>
       </c>
-      <c r="K21" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K21" s="69">
+        <v>1.3363999999999998</v>
       </c>
       <c r="L21" s="28"/>
     </row>
-    <row r="22" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
       <c r="B22" s="39">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
@@ -4296,14 +2509,13 @@
       <c r="J22" s="27">
         <v>1</v>
       </c>
-      <c r="K22" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K22" s="68">
+        <v>0.95499999999999996</v>
       </c>
       <c r="L22" s="27"/>
     </row>
-    <row r="23" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
       <c r="B23" s="41">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4332,14 +2544,13 @@
       <c r="J23" s="28">
         <v>1</v>
       </c>
-      <c r="K23" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K23" s="69">
+        <v>1.3919999999999999</v>
       </c>
       <c r="L23" s="28"/>
     </row>
-    <row r="24" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+    <row r="24" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
       <c r="B24" s="39">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
@@ -4368,14 +2579,13 @@
       <c r="J24" s="27">
         <v>1</v>
       </c>
-      <c r="K24" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K24" s="68">
+        <v>1.1179999999999999</v>
       </c>
       <c r="L24" s="27"/>
     </row>
-    <row r="25" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
+    <row r="25" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
       <c r="B25" s="41">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -4404,14 +2614,13 @@
       <c r="J25" s="28">
         <v>1</v>
       </c>
-      <c r="K25" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K25" s="69">
+        <v>1.4049999999999998</v>
       </c>
       <c r="L25" s="28"/>
     </row>
-    <row r="26" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
+    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
       <c r="B26" s="39">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
@@ -4440,14 +2649,13 @@
       <c r="J26" s="27">
         <v>1</v>
       </c>
-      <c r="K26" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K26" s="68">
+        <v>1.0549999999999999</v>
       </c>
       <c r="L26" s="27"/>
     </row>
-    <row r="27" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
+    <row r="27" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
       <c r="B27" s="41">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -4476,14 +2684,13 @@
       <c r="J27" s="28">
         <v>2</v>
       </c>
-      <c r="K27" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K27" s="69">
+        <v>2.2290000000000001</v>
       </c>
       <c r="L27" s="28"/>
     </row>
-    <row r="28" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
+    <row r="28" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
       <c r="B28" s="39">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
@@ -4512,14 +2719,13 @@
       <c r="J28" s="27">
         <v>13</v>
       </c>
-      <c r="K28" s="27">
-        <f t="shared" si="1"/>
-        <v>26</v>
+      <c r="K28" s="68">
+        <v>1.1459999999999999</v>
       </c>
       <c r="L28" s="27"/>
     </row>
-    <row r="29" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
+    <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
       <c r="B29" s="41">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4548,14 +2754,13 @@
       <c r="J29" s="28">
         <v>1</v>
       </c>
-      <c r="K29" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K29" s="69">
+        <v>1.4550000000000001</v>
       </c>
       <c r="L29" s="28"/>
     </row>
-    <row r="30" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
       <c r="B30" s="39">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
@@ -4584,14 +2789,13 @@
       <c r="J30" s="27">
         <v>4</v>
       </c>
-      <c r="K30" s="27">
-        <f t="shared" si="1"/>
-        <v>8</v>
+      <c r="K30" s="68">
+        <v>1.1499999999999999</v>
       </c>
       <c r="L30" s="27"/>
     </row>
-    <row r="31" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="44"/>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
       <c r="B31" s="41">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -4620,14 +2824,13 @@
       <c r="J31" s="28">
         <v>2</v>
       </c>
-      <c r="K31" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K31" s="69">
+        <v>1.2999999999999998</v>
       </c>
       <c r="L31" s="28"/>
     </row>
-    <row r="32" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
       <c r="B32" s="39">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
@@ -4656,14 +2859,13 @@
       <c r="J32" s="27">
         <v>1</v>
       </c>
-      <c r="K32" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K32" s="68">
+        <v>1.268</v>
       </c>
       <c r="L32" s="27"/>
     </row>
-    <row r="33" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
+    <row r="33" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
       <c r="B33" s="39">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
@@ -4692,14 +2894,13 @@
       <c r="J33" s="28">
         <v>1</v>
       </c>
-      <c r="K33" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K33" s="69">
+        <v>2.4249999999999998</v>
       </c>
       <c r="L33" s="28"/>
     </row>
-    <row r="34" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
       <c r="B34" s="41">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -4728,14 +2929,13 @@
       <c r="J34" s="28">
         <v>2</v>
       </c>
-      <c r="K34" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K34" s="68">
+        <v>1.292</v>
       </c>
       <c r="L34" s="27"/>
     </row>
-    <row r="35" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
       <c r="B35" s="39">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
@@ -4764,14 +2964,13 @@
       <c r="J35" s="27">
         <v>1</v>
       </c>
-      <c r="K35" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K35" s="68">
+        <v>1.2439999999999998</v>
       </c>
       <c r="L35" s="28"/>
     </row>
-    <row r="36" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
+    <row r="36" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
       <c r="B36" s="41">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -4800,14 +2999,13 @@
       <c r="J36" s="28">
         <v>2</v>
       </c>
-      <c r="K36" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K36" s="68">
+        <v>1.115</v>
       </c>
       <c r="L36" s="27"/>
     </row>
-    <row r="37" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="44"/>
+    <row r="37" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
       <c r="B37" s="39">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
@@ -4836,14 +3034,13 @@
       <c r="J37" s="27">
         <v>3</v>
       </c>
-      <c r="K37" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K37" s="68">
+        <v>1.1299999999999999</v>
       </c>
       <c r="L37" s="28"/>
     </row>
-    <row r="38" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
+    <row r="38" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
       <c r="B38" s="41">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4872,14 +3069,13 @@
       <c r="J38" s="28">
         <v>2</v>
       </c>
-      <c r="K38" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K38" s="68">
+        <v>1.202</v>
       </c>
       <c r="L38" s="27"/>
     </row>
-    <row r="39" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A39" s="44"/>
+    <row r="39" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
       <c r="B39" s="39">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
@@ -4908,14 +3104,13 @@
       <c r="J39" s="27">
         <v>3</v>
       </c>
-      <c r="K39" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K39" s="68">
+        <v>1.272</v>
       </c>
       <c r="L39" s="28"/>
     </row>
-    <row r="40" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="44"/>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
       <c r="B40" s="41">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4944,14 +3139,13 @@
       <c r="J40" s="28">
         <v>2</v>
       </c>
-      <c r="K40" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K40" s="68">
+        <v>1.1099999999999999</v>
       </c>
       <c r="L40" s="27"/>
     </row>
-    <row r="41" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A41" s="44"/>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
       <c r="B41" s="39">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
@@ -4980,14 +3174,13 @@
       <c r="J41" s="27">
         <v>3</v>
       </c>
-      <c r="K41" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K41" s="68">
+        <v>1.2959999999999998</v>
       </c>
       <c r="L41" s="28"/>
     </row>
-    <row r="42" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
       <c r="B42" s="41">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -5014,14 +3207,13 @@
       <c r="J42" s="28">
         <v>3</v>
       </c>
-      <c r="K42" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K42" s="68">
+        <v>0.76999999999999991</v>
       </c>
       <c r="L42" s="27"/>
     </row>
-    <row r="43" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="44"/>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
       <c r="B43" s="39">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
@@ -5050,14 +3242,13 @@
       <c r="J43" s="27">
         <v>2</v>
       </c>
-      <c r="K43" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K43" s="68">
+        <v>0.82</v>
       </c>
       <c r="L43" s="28"/>
     </row>
-    <row r="44" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
+    <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
       <c r="B44" s="41">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -5086,14 +3277,13 @@
       <c r="J44" s="28">
         <v>3</v>
       </c>
-      <c r="K44" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K44" s="68">
+        <v>1.2439999999999998</v>
       </c>
       <c r="L44" s="27"/>
     </row>
-    <row r="45" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A45" s="44"/>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
       <c r="B45" s="39">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
@@ -5122,14 +3312,13 @@
       <c r="J45" s="27">
         <v>2</v>
       </c>
-      <c r="K45" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K45" s="68">
+        <v>1.198</v>
       </c>
       <c r="L45" s="28"/>
     </row>
-    <row r="46" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A46" s="44"/>
+    <row r="46" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
       <c r="B46" s="41">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -5158,14 +3347,13 @@
       <c r="J46" s="28">
         <v>3</v>
       </c>
-      <c r="K46" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K46" s="68">
+        <v>1.3039999999999998</v>
       </c>
       <c r="L46" s="27"/>
     </row>
-    <row r="47" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="44"/>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
       <c r="B47" s="39">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
@@ -5194,14 +3382,13 @@
       <c r="J47" s="27">
         <v>2</v>
       </c>
-      <c r="K47" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K47" s="68">
+        <v>1.2559999999999998</v>
       </c>
       <c r="L47" s="28"/>
     </row>
-    <row r="48" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A48" s="44"/>
+    <row r="48" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
       <c r="B48" s="41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -5230,14 +3417,13 @@
       <c r="J48" s="28">
         <v>2</v>
       </c>
-      <c r="K48" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K48" s="68">
+        <v>1.3479999999999999</v>
       </c>
       <c r="L48" s="27"/>
     </row>
-    <row r="49" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="44"/>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
       <c r="B49" s="39">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
@@ -5266,14 +3452,13 @@
       <c r="J49" s="27">
         <v>3</v>
       </c>
-      <c r="K49" s="27">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="K49" s="68">
+        <v>1.216</v>
       </c>
       <c r="L49" s="28"/>
     </row>
-    <row r="50" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A50" s="44"/>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
       <c r="B50" s="41">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -5302,14 +3487,13 @@
       <c r="J50" s="28">
         <v>1</v>
       </c>
-      <c r="K50" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K50" s="68">
+        <v>1.2879999999999998</v>
       </c>
       <c r="L50" s="27"/>
     </row>
-    <row r="51" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A51" s="44"/>
+    <row r="51" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
       <c r="B51" s="39">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
@@ -5338,14 +3522,13 @@
       <c r="J51" s="27">
         <v>1</v>
       </c>
-      <c r="K51" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K51" s="68">
+        <v>0.8899999999999999</v>
       </c>
       <c r="L51" s="28"/>
     </row>
-    <row r="52" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A52" s="44"/>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
       <c r="B52" s="41">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -5374,14 +3557,13 @@
       <c r="J52" s="28">
         <v>1</v>
       </c>
-      <c r="K52" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K52" s="68">
+        <v>1.472</v>
       </c>
       <c r="L52" s="27"/>
     </row>
-    <row r="53" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A53" s="44"/>
+    <row r="53" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
       <c r="B53" s="39">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
@@ -5410,14 +3592,13 @@
       <c r="J53" s="27">
         <v>1</v>
       </c>
-      <c r="K53" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K53" s="68">
+        <v>1.1339999999999999</v>
       </c>
       <c r="L53" s="28"/>
     </row>
-    <row r="54" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A54" s="44"/>
+    <row r="54" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
       <c r="B54" s="41">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -5446,14 +3627,13 @@
       <c r="J54" s="28">
         <v>1</v>
       </c>
-      <c r="K54" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K54" s="68">
+        <v>1.3239999999999998</v>
       </c>
       <c r="L54" s="27"/>
     </row>
-    <row r="55" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A55" s="44"/>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
       <c r="B55" s="39">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
@@ -5482,14 +3662,13 @@
       <c r="J55" s="27">
         <v>1</v>
       </c>
-      <c r="K55" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K55" s="68">
+        <v>1.204</v>
       </c>
       <c r="L55" s="28"/>
     </row>
-    <row r="56" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
+    <row r="56" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
       <c r="B56" s="41">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -5518,14 +3697,13 @@
       <c r="J56" s="28">
         <v>1</v>
       </c>
-      <c r="K56" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K56" s="68">
+        <v>1.1739999999999999</v>
       </c>
       <c r="L56" s="27"/>
     </row>
-    <row r="57" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A57" s="44"/>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
       <c r="B57" s="41">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -5554,14 +3732,13 @@
       <c r="J57" s="28">
         <v>1</v>
       </c>
-      <c r="K57" s="27">
-        <f t="shared" si="1"/>
-        <v>2</v>
+      <c r="K57" s="69">
+        <v>1.42</v>
       </c>
       <c r="L57" s="28"/>
     </row>
-    <row r="58" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A58" s="44"/>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
       <c r="B58" s="39">
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
@@ -5590,14 +3767,13 @@
       <c r="J58" s="27">
         <v>2</v>
       </c>
-      <c r="K58" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="K58" s="68">
+        <v>1.208</v>
       </c>
       <c r="L58" s="27"/>
     </row>
-    <row r="59" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="44"/>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
       <c r="B59" s="41">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -5626,11 +3802,10 @@
       <c r="J59" s="43">
         <v>2</v>
       </c>
-      <c r="K59" s="27">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L59" s="28"/>
+      <c r="K59" s="76" t="s">
+        <v>236</v>
+      </c>
+      <c r="L59" s="27"/>
     </row>
     <row r="60" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
@@ -5662,13 +3837,2259 @@
       <c r="J60" s="27">
         <v>9</v>
       </c>
+      <c r="K60" s="68">
+        <v>11.042</v>
+      </c>
+      <c r="L60" s="27"/>
+    </row>
+    <row r="61" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="49">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C61" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="D61" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E61" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F61" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="G61" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="I61" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="J61" s="51">
+        <v>3</v>
+      </c>
+      <c r="K61" s="77">
+        <v>1.839</v>
+      </c>
+      <c r="L61" s="27"/>
+    </row>
+    <row r="62" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="52"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="I62" s="73"/>
+      <c r="J62" s="73"/>
+      <c r="K62" s="74">
+        <f>SUM(K10:K61)</f>
+        <v>74.817499999999995</v>
+      </c>
+      <c r="L62" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="H62:J62"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="29"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="66"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="67"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="67"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="67"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="67"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="67"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="K9" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="44"/>
+      <c r="B10" s="39">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="J10" s="27">
+        <v>4</v>
+      </c>
+      <c r="K10" s="27">
+        <f>J10*2</f>
+        <v>8</v>
+      </c>
+      <c r="L10" s="68">
+        <v>1.35</v>
+      </c>
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44"/>
+      <c r="B11" s="41">
+        <f t="shared" ref="B11:B61" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="28">
+        <v>4</v>
+      </c>
+      <c r="K11" s="27">
+        <f t="shared" ref="K11:K61" si="1">J11*2</f>
+        <v>8</v>
+      </c>
+      <c r="L11" s="68">
+        <v>1.3279999999999998</v>
+      </c>
+      <c r="M11" s="28"/>
+    </row>
+    <row r="12" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="44"/>
+      <c r="B12" s="39">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="27">
+        <v>1</v>
+      </c>
+      <c r="K12" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L12" s="68">
+        <v>1.175</v>
+      </c>
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="44"/>
+      <c r="B13" s="41">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" s="28">
+        <v>1</v>
+      </c>
+      <c r="K13" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L13" s="68">
+        <v>1.05</v>
+      </c>
+      <c r="M13" s="28"/>
+    </row>
+    <row r="14" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
+      <c r="B14" s="39">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="27">
+        <v>1</v>
+      </c>
+      <c r="K14" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L14" s="68">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44"/>
+      <c r="B15" s="41">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="28">
+        <v>2</v>
+      </c>
+      <c r="K15" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L15" s="68">
+        <v>1.3080000000000001</v>
+      </c>
+      <c r="M15" s="28"/>
+    </row>
+    <row r="16" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44"/>
+      <c r="B16" s="39">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="J16" s="27">
+        <v>1</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L16" s="68">
+        <v>1.2</v>
+      </c>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="44"/>
+      <c r="B17" s="41">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="J17" s="28">
+        <v>1</v>
+      </c>
+      <c r="K17" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L17" s="68">
+        <v>1.21</v>
+      </c>
+      <c r="M17" s="28"/>
+    </row>
+    <row r="18" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="39">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="J18" s="27">
+        <v>1</v>
+      </c>
+      <c r="K18" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L18" s="68">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="44"/>
+      <c r="B19" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="J19" s="28">
+        <v>2</v>
+      </c>
+      <c r="K19" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L19" s="68">
+        <v>2.8185000000000002</v>
+      </c>
+      <c r="M19" s="28"/>
+    </row>
+    <row r="20" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="39">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="J20" s="27">
+        <v>1</v>
+      </c>
+      <c r="K20" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L20" s="68">
+        <v>1.395</v>
+      </c>
+      <c r="M20" s="27"/>
+    </row>
+    <row r="21" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="44"/>
+      <c r="B21" s="41">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="28">
+        <v>1</v>
+      </c>
+      <c r="K21" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L21" s="68">
+        <v>1.7045999999999999</v>
+      </c>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="44"/>
+      <c r="B22" s="39">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="27">
+        <v>1</v>
+      </c>
+      <c r="K22" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L22" s="68">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="M22" s="27"/>
+    </row>
+    <row r="23" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="44"/>
+      <c r="B23" s="41">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="J23" s="28">
+        <v>1</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L23" s="68">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A24" s="44"/>
+      <c r="B24" s="39">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J24" s="27">
+        <v>1</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L24" s="68">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="M24" s="27"/>
+    </row>
+    <row r="25" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="41">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="J25" s="28">
+        <v>1</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L25" s="68">
+        <v>1.4550000000000001</v>
+      </c>
+      <c r="M25" s="28"/>
+    </row>
+    <row r="26" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="44"/>
+      <c r="B26" s="39">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J26" s="27">
+        <v>1</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L26" s="68">
+        <v>1.2825</v>
+      </c>
+      <c r="M26" s="27"/>
+    </row>
+    <row r="27" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="41">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="J27" s="28">
+        <v>2</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="68">
+        <v>2.2789999999999999</v>
+      </c>
+      <c r="M27" s="28"/>
+    </row>
+    <row r="28" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="39">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="J28" s="27">
+        <v>13</v>
+      </c>
+      <c r="K28" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="L28" s="68">
+        <v>1.6419999999999999</v>
+      </c>
+      <c r="M28" s="27"/>
+    </row>
+    <row r="29" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="44"/>
+      <c r="B29" s="41">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="J29" s="28">
+        <v>1</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L29" s="68">
+        <v>1.5049999999999999</v>
+      </c>
+      <c r="M29" s="28"/>
+    </row>
+    <row r="30" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A30" s="44"/>
+      <c r="B30" s="39">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="J30" s="27">
+        <v>4</v>
+      </c>
+      <c r="K30" s="27">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L30" s="68">
+        <v>1.2</v>
+      </c>
+      <c r="M30" s="27"/>
+    </row>
+    <row r="31" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="44"/>
+      <c r="B31" s="41">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="J31" s="28">
+        <v>2</v>
+      </c>
+      <c r="K31" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L31" s="68">
+        <v>1.35</v>
+      </c>
+      <c r="M31" s="28"/>
+    </row>
+    <row r="32" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="39">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="J32" s="27">
+        <v>1</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L32" s="68">
+        <v>1.3180000000000001</v>
+      </c>
+      <c r="M32" s="27"/>
+    </row>
+    <row r="33" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="44"/>
+      <c r="B33" s="39">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="48" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="J33" s="28">
+        <v>1</v>
+      </c>
+      <c r="K33" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L33" s="68">
+        <v>2.4749999999999996</v>
+      </c>
+      <c r="M33" s="28"/>
+    </row>
+    <row r="34" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="41">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="J34" s="28">
+        <v>2</v>
+      </c>
+      <c r="K34" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L34" s="68">
+        <v>1.3420000000000001</v>
+      </c>
+      <c r="M34" s="27"/>
+    </row>
+    <row r="35" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="44"/>
+      <c r="B35" s="39">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I35" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="J35" s="27">
+        <v>1</v>
+      </c>
+      <c r="K35" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L35" s="68">
+        <v>1.294</v>
+      </c>
+      <c r="M35" s="28"/>
+    </row>
+    <row r="36" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="44"/>
+      <c r="B36" s="41">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" s="28">
+        <v>2</v>
+      </c>
+      <c r="K36" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L36" s="68">
+        <v>1.165</v>
+      </c>
+      <c r="M36" s="27"/>
+    </row>
+    <row r="37" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="44"/>
+      <c r="B37" s="39">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H37" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="J37" s="27">
+        <v>3</v>
+      </c>
+      <c r="K37" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L37" s="68">
+        <v>1.18</v>
+      </c>
+      <c r="M37" s="28"/>
+    </row>
+    <row r="38" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="44"/>
+      <c r="B38" s="41">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="J38" s="28">
+        <v>2</v>
+      </c>
+      <c r="K38" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L38" s="68">
+        <v>1.252</v>
+      </c>
+      <c r="M38" s="27"/>
+    </row>
+    <row r="39" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A39" s="44"/>
+      <c r="B39" s="39">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="J39" s="27">
+        <v>3</v>
+      </c>
+      <c r="K39" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L39" s="68">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="M39" s="28"/>
+    </row>
+    <row r="40" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="44"/>
+      <c r="B40" s="41">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="J40" s="28">
+        <v>2</v>
+      </c>
+      <c r="K40" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L40" s="68">
+        <v>1.1600000000000001</v>
+      </c>
+      <c r="M40" s="27"/>
+    </row>
+    <row r="41" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A41" s="44"/>
+      <c r="B41" s="39">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="H41" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I41" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="J41" s="27">
+        <v>3</v>
+      </c>
+      <c r="K41" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L41" s="68">
+        <v>1.3460000000000001</v>
+      </c>
+      <c r="M41" s="28"/>
+    </row>
+    <row r="42" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="44"/>
+      <c r="B42" s="41">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="40"/>
+      <c r="D42" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I42" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="J42" s="28">
+        <v>3</v>
+      </c>
+      <c r="K42" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L42" s="68">
+        <v>0.82</v>
+      </c>
+      <c r="M42" s="27"/>
+    </row>
+    <row r="43" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="44"/>
+      <c r="B43" s="39">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H43" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="J43" s="27">
+        <v>2</v>
+      </c>
+      <c r="K43" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L43" s="68">
+        <v>0.87</v>
+      </c>
+      <c r="M43" s="28"/>
+    </row>
+    <row r="44" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A44" s="44"/>
+      <c r="B44" s="41">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="J44" s="28">
+        <v>3</v>
+      </c>
+      <c r="K44" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L44" s="68">
+        <v>1.294</v>
+      </c>
+      <c r="M44" s="27"/>
+    </row>
+    <row r="45" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A45" s="44"/>
+      <c r="B45" s="39">
+        <f>ROW(B45) - ROW($B$9)</f>
+        <v>36</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I45" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="J45" s="27">
+        <v>2</v>
+      </c>
+      <c r="K45" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L45" s="68">
+        <v>1.248</v>
+      </c>
+      <c r="M45" s="28"/>
+    </row>
+    <row r="46" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A46" s="44"/>
+      <c r="B46" s="41">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I46" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="J46" s="28">
+        <v>3</v>
+      </c>
+      <c r="K46" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L46" s="68">
+        <v>1.3540000000000001</v>
+      </c>
+      <c r="M46" s="27"/>
+    </row>
+    <row r="47" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="44"/>
+      <c r="B47" s="39">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="H47" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="J47" s="27">
+        <v>2</v>
+      </c>
+      <c r="K47" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L47" s="68">
+        <v>1.306</v>
+      </c>
+      <c r="M47" s="28"/>
+    </row>
+    <row r="48" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A48" s="44"/>
+      <c r="B48" s="41">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="J48" s="28">
+        <v>2</v>
+      </c>
+      <c r="K48" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L48" s="68">
+        <v>1.3979999999999999</v>
+      </c>
+      <c r="M48" s="27"/>
+    </row>
+    <row r="49" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="44"/>
+      <c r="B49" s="39">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="H49" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="J49" s="27">
+        <v>3</v>
+      </c>
+      <c r="K49" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L49" s="68">
+        <v>1.266</v>
+      </c>
+      <c r="M49" s="28"/>
+    </row>
+    <row r="50" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="44"/>
+      <c r="B50" s="41">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I50" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="J50" s="28">
+        <v>1</v>
+      </c>
+      <c r="K50" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L50" s="68">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="M50" s="27"/>
+    </row>
+    <row r="51" spans="1:17" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A51" s="44"/>
+      <c r="B51" s="39">
+        <f>ROW(B51) - ROW($B$9)</f>
+        <v>42</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="I51" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="J51" s="27">
+        <v>1</v>
+      </c>
+      <c r="K51" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L51" s="68">
+        <v>0.94</v>
+      </c>
+      <c r="M51" s="28"/>
+    </row>
+    <row r="52" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A52" s="44"/>
+      <c r="B52" s="41">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I52" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="J52" s="28">
+        <v>1</v>
+      </c>
+      <c r="K52" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L52" s="68">
+        <v>1.522</v>
+      </c>
+      <c r="M52" s="27"/>
+    </row>
+    <row r="53" spans="1:17" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A53" s="44"/>
+      <c r="B53" s="39">
+        <f>ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G53" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H53" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="J53" s="27">
+        <v>1</v>
+      </c>
+      <c r="K53" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L53" s="68">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="M53" s="28"/>
+    </row>
+    <row r="54" spans="1:17" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A54" s="44"/>
+      <c r="B54" s="41">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I54" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="J54" s="28">
+        <v>1</v>
+      </c>
+      <c r="K54" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L54" s="68">
+        <v>1.3740000000000001</v>
+      </c>
+      <c r="M54" s="27"/>
+    </row>
+    <row r="55" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A55" s="44"/>
+      <c r="B55" s="39">
+        <f>ROW(B55) - ROW($B$9)</f>
+        <v>46</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="H55" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I55" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="J55" s="27">
+        <v>1</v>
+      </c>
+      <c r="K55" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L55" s="68">
+        <v>1.254</v>
+      </c>
+      <c r="M55" s="28"/>
+    </row>
+    <row r="56" spans="1:17" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A56" s="44"/>
+      <c r="B56" s="41">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="I56" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="J56" s="28">
+        <v>1</v>
+      </c>
+      <c r="K56" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L56" s="68">
+        <v>1.224</v>
+      </c>
+      <c r="M56" s="27"/>
+    </row>
+    <row r="57" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A57" s="44"/>
+      <c r="B57" s="41">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H57" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="I57" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="J57" s="28">
+        <v>1</v>
+      </c>
+      <c r="K57" s="27">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L57" s="68">
+        <v>1.47</v>
+      </c>
+      <c r="M57" s="28"/>
+    </row>
+    <row r="58" spans="1:17" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="44"/>
+      <c r="B58" s="39">
+        <f>ROW(B58) - ROW($B$9)</f>
+        <v>49</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="F58" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G58" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H58" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I58" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="J58" s="27">
+        <v>2</v>
+      </c>
+      <c r="K58" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L58" s="68">
+        <v>1.258</v>
+      </c>
+      <c r="M58" s="27"/>
+    </row>
+    <row r="59" spans="1:17" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="44"/>
+      <c r="B59" s="41">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="G59" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="I59" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="J59" s="43">
+        <v>2</v>
+      </c>
+      <c r="K59" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L59" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="M59" s="28"/>
+    </row>
+    <row r="60" spans="1:17" ht="48" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="39">
+        <f>ROW(B60) - ROW($B$9)</f>
+        <v>51</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F60" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="G60" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="H60" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="I60" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J60" s="27">
+        <v>9</v>
+      </c>
       <c r="K60" s="27">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="L60" s="28"/>
-    </row>
-    <row r="61" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L60" s="68">
+        <v>11.092000000000001</v>
+      </c>
+      <c r="M60" s="28"/>
+      <c r="Q60" s="45"/>
+    </row>
+    <row r="61" spans="1:17" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="41">
         <f t="shared" si="0"/>
@@ -5702,9 +6123,13 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L61" s="28"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L61" s="68">
+        <v>1.889</v>
+      </c>
+      <c r="M61" s="28"/>
+      <c r="Q61" s="45"/>
+    </row>
+    <row r="62" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="58"/>
       <c r="C62" s="59"/>
       <c r="D62" s="60"/>
@@ -5712,15 +6137,35 @@
       <c r="F62" s="62"/>
       <c r="G62" s="63"/>
       <c r="H62" s="62"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63"/>
-      <c r="L62" s="63"/>
+      <c r="I62" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="J62" s="73"/>
+      <c r="K62" s="73"/>
+      <c r="L62" s="74">
+        <f>SUM(L10:L61)</f>
+        <v>79.136599999999973</v>
+      </c>
+      <c r="M62" s="63"/>
+      <c r="Q62" s="45"/>
+    </row>
+    <row r="63" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="72" t="s">
+        <v>260</v>
+      </c>
+      <c r="J63" s="73"/>
+      <c r="K63" s="73"/>
+      <c r="L63" s="75">
+        <f>L62/2</f>
+        <v>39.568299999999986</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="L3:L8"/>
+  <mergeCells count="4">
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5729,7 +6174,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -5742,10 +6187,11 @@
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.140625" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5758,8 +6204,9 @@
       <c r="J1" s="65"/>
       <c r="K1" s="65"/>
       <c r="L1" s="65"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="65"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="18"/>
       <c r="C2" s="30"/>
@@ -5775,9 +6222,10 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="29"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="3"/>
+      <c r="M2" s="29"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="19"/>
       <c r="C3" s="31"/>
@@ -5793,9 +6241,10 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="66"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4"/>
+      <c r="M3" s="66"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="19"/>
       <c r="C4" s="31"/>
@@ -5811,9 +6260,10 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="46"/>
-      <c r="L4" s="67"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="46"/>
+      <c r="M4" s="67"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="19"/>
       <c r="C5" s="31"/>
@@ -5829,9 +6279,10 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="46"/>
-      <c r="L5" s="67"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="46"/>
+      <c r="M5" s="67"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="20"/>
       <c r="C6" s="32"/>
@@ -5843,9 +6294,10 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="46"/>
-      <c r="L6" s="67"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="46"/>
+      <c r="M6" s="67"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="21"/>
       <c r="C7" s="33"/>
@@ -5857,9 +6309,10 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="67"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="7"/>
+      <c r="M7" s="67"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="23"/>
       <c r="C8" s="34"/>
@@ -5871,9 +6324,10 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="67"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="7"/>
+      <c r="M8" s="67"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="26" t="s">
         <v>4</v>
@@ -5906,10 +6360,13 @@
         <v>246</v>
       </c>
       <c r="L9" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="M9" s="26" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="39">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -5943,9 +6400,12 @@
         <f>J10*5</f>
         <v>20</v>
       </c>
-      <c r="L10" s="27"/>
-    </row>
-    <row r="11" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="68">
+        <v>1.52</v>
+      </c>
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B61" si="0">ROW(B11) - ROW($B$9)</f>
@@ -5979,9 +6439,12 @@
         <f t="shared" ref="K11" si="1">J11*5</f>
         <v>20</v>
       </c>
-      <c r="L11" s="28"/>
-    </row>
-    <row r="12" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="69">
+        <v>2.0760000000000001</v>
+      </c>
+      <c r="M11" s="28"/>
+    </row>
+    <row r="12" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
       <c r="B12" s="39">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -6015,9 +6478,12 @@
         <f>J12*5</f>
         <v>5</v>
       </c>
-      <c r="L12" s="27"/>
-    </row>
-    <row r="13" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="68">
+        <v>1.3450000000000002</v>
+      </c>
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44"/>
       <c r="B13" s="41">
         <f t="shared" si="0"/>
@@ -6051,9 +6517,12 @@
         <f t="shared" ref="K13" si="2">J13*5</f>
         <v>5</v>
       </c>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L13" s="69">
+        <v>1.22</v>
+      </c>
+      <c r="M13" s="28"/>
+    </row>
+    <row r="14" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
       <c r="B14" s="39">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -6087,9 +6556,12 @@
         <f>J14*5</f>
         <v>5</v>
       </c>
-      <c r="L14" s="27"/>
-    </row>
-    <row r="15" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="68">
+        <v>1.3540000000000001</v>
+      </c>
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
       <c r="B15" s="41">
         <f t="shared" si="0"/>
@@ -6123,9 +6595,12 @@
         <f t="shared" ref="K15" si="3">J15*5</f>
         <v>10</v>
       </c>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="69">
+        <v>1.4780000000000002</v>
+      </c>
+      <c r="M15" s="28"/>
+    </row>
+    <row r="16" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="44"/>
       <c r="B16" s="39">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -6159,9 +6634,12 @@
         <f>J16*5</f>
         <v>5</v>
       </c>
-      <c r="L16" s="27"/>
-    </row>
-    <row r="17" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L16" s="68">
+        <v>1.37</v>
+      </c>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="44"/>
       <c r="B17" s="41">
         <f t="shared" si="0"/>
@@ -6195,9 +6673,12 @@
         <f t="shared" ref="K17" si="4">J17*5</f>
         <v>5</v>
       </c>
-      <c r="L17" s="28"/>
-    </row>
-    <row r="18" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L17" s="69">
+        <v>1.38</v>
+      </c>
+      <c r="M17" s="28"/>
+    </row>
+    <row r="18" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
       <c r="B18" s="39">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -6231,9 +6712,12 @@
         <f>J18*5</f>
         <v>5</v>
       </c>
-      <c r="L18" s="27"/>
-    </row>
-    <row r="19" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L18" s="68">
+        <v>1.3</v>
+      </c>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="41">
         <f t="shared" si="0"/>
@@ -6267,9 +6751,12 @@
         <f t="shared" ref="K19" si="5">J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="28"/>
-    </row>
-    <row r="20" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L19" s="69">
+        <v>5.4706999999999999</v>
+      </c>
+      <c r="M19" s="28"/>
+    </row>
+    <row r="20" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
       <c r="B20" s="39">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -6303,9 +6790,12 @@
         <f>J20*5</f>
         <v>5</v>
       </c>
-      <c r="L20" s="27"/>
-    </row>
-    <row r="21" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L20" s="68">
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="M20" s="27"/>
+    </row>
+    <row r="21" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
       <c r="B21" s="41">
         <f t="shared" si="0"/>
@@ -6339,9 +6829,12 @@
         <f t="shared" ref="K21" si="6">J21*5</f>
         <v>5</v>
       </c>
-      <c r="L21" s="28"/>
-    </row>
-    <row r="22" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="69">
+        <v>2.8291999999999997</v>
+      </c>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="39">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -6375,9 +6868,12 @@
         <f>J22*5</f>
         <v>5</v>
       </c>
-      <c r="L22" s="27"/>
-    </row>
-    <row r="23" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L22" s="68">
+        <v>1.175</v>
+      </c>
+      <c r="M22" s="27"/>
+    </row>
+    <row r="23" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
       <c r="B23" s="41">
         <f t="shared" si="0"/>
@@ -6411,9 +6907,12 @@
         <f t="shared" ref="K23" si="7">J23*5</f>
         <v>5</v>
       </c>
-      <c r="L23" s="28"/>
-    </row>
-    <row r="24" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L23" s="69">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
       <c r="B24" s="39">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -6447,9 +6946,12 @@
         <f>J24*5</f>
         <v>5</v>
       </c>
-      <c r="L24" s="27"/>
-    </row>
-    <row r="25" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L24" s="68">
+        <v>1.756</v>
+      </c>
+      <c r="M24" s="27"/>
+    </row>
+    <row r="25" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
       <c r="B25" s="41">
         <f t="shared" si="0"/>
@@ -6483,9 +6985,12 @@
         <f t="shared" ref="K25" si="8">J25*5</f>
         <v>5</v>
       </c>
-      <c r="L25" s="28"/>
-    </row>
-    <row r="26" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L25" s="69">
+        <v>1.625</v>
+      </c>
+      <c r="M25" s="28"/>
+    </row>
+    <row r="26" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
       <c r="B26" s="39">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -6519,9 +7024,12 @@
         <f>J26*5</f>
         <v>5</v>
       </c>
-      <c r="L26" s="27"/>
-    </row>
-    <row r="27" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L26" s="68">
+        <v>1.9849999999999999</v>
+      </c>
+      <c r="M26" s="27"/>
+    </row>
+    <row r="27" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
       <c r="B27" s="41">
         <f t="shared" si="0"/>
@@ -6555,9 +7063,12 @@
         <f t="shared" ref="K27" si="9">J27*5</f>
         <v>10</v>
       </c>
-      <c r="L27" s="28"/>
-    </row>
-    <row r="28" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L27" s="69">
+        <v>5.5070000000000006</v>
+      </c>
+      <c r="M27" s="28"/>
+    </row>
+    <row r="28" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
       <c r="B28" s="39">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -6591,9 +7102,12 @@
         <f>J28*5</f>
         <v>65</v>
       </c>
-      <c r="L28" s="27"/>
-    </row>
-    <row r="29" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L28" s="68">
+        <v>2.7040000000000002</v>
+      </c>
+      <c r="M28" s="27"/>
+    </row>
+    <row r="29" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
       <c r="B29" s="41">
         <f t="shared" si="0"/>
@@ -6627,9 +7141,12 @@
         <f t="shared" ref="K29" si="10">J29*5</f>
         <v>5</v>
       </c>
-      <c r="L29" s="28"/>
-    </row>
-    <row r="30" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L29" s="69">
+        <v>1.675</v>
+      </c>
+      <c r="M29" s="28"/>
+    </row>
+    <row r="30" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
       <c r="B30" s="39">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -6663,9 +7180,12 @@
         <f>J30*5</f>
         <v>20</v>
       </c>
-      <c r="L30" s="27"/>
-    </row>
-    <row r="31" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L30" s="68">
+        <v>1.8199999999999998</v>
+      </c>
+      <c r="M30" s="27"/>
+    </row>
+    <row r="31" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
       <c r="B31" s="41">
         <f t="shared" si="0"/>
@@ -6699,9 +7219,12 @@
         <f t="shared" ref="K31" si="11">J31*5</f>
         <v>10</v>
       </c>
-      <c r="L31" s="28"/>
-    </row>
-    <row r="32" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L31" s="69">
+        <v>1.52</v>
+      </c>
+      <c r="M31" s="28"/>
+    </row>
+    <row r="32" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
       <c r="B32" s="39">
         <f>ROW(B32) - ROW($B$9)</f>
@@ -6735,9 +7258,12 @@
         <f>J32*5</f>
         <v>5</v>
       </c>
-      <c r="L32" s="27"/>
-    </row>
-    <row r="33" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L32" s="68">
+        <v>1.488</v>
+      </c>
+      <c r="M32" s="27"/>
+    </row>
+    <row r="33" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
       <c r="B33" s="39"/>
       <c r="C33" s="40" t="s">
@@ -6768,9 +7294,12 @@
         <f t="shared" ref="K33:K34" si="12">J33*5</f>
         <v>5</v>
       </c>
-      <c r="L33" s="28"/>
-    </row>
-    <row r="34" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L33" s="68">
+        <v>4.37</v>
+      </c>
+      <c r="M33" s="28"/>
+    </row>
+    <row r="34" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
       <c r="B34" s="41">
         <f t="shared" si="0"/>
@@ -6804,9 +7333,12 @@
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="L34" s="27"/>
-    </row>
-    <row r="35" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L34" s="68">
+        <v>1.512</v>
+      </c>
+      <c r="M34" s="27"/>
+    </row>
+    <row r="35" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="44"/>
       <c r="B35" s="39">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -6840,9 +7372,12 @@
         <f>J35*5</f>
         <v>5</v>
       </c>
-      <c r="L35" s="28"/>
-    </row>
-    <row r="36" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L35" s="68">
+        <v>1.464</v>
+      </c>
+      <c r="M35" s="28"/>
+    </row>
+    <row r="36" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="44"/>
       <c r="B36" s="41">
         <f t="shared" si="0"/>
@@ -6876,9 +7411,12 @@
         <f t="shared" ref="K36" si="13">J36*5</f>
         <v>10</v>
       </c>
-      <c r="L36" s="27"/>
-    </row>
-    <row r="37" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L36" s="68">
+        <v>1.335</v>
+      </c>
+      <c r="M36" s="27"/>
+    </row>
+    <row r="37" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="44"/>
       <c r="B37" s="39">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -6912,9 +7450,12 @@
         <f>J37*5</f>
         <v>15</v>
       </c>
-      <c r="L37" s="28"/>
-    </row>
-    <row r="38" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L37" s="68">
+        <v>1.7799999999999998</v>
+      </c>
+      <c r="M37" s="28"/>
+    </row>
+    <row r="38" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
       <c r="B38" s="41">
         <f t="shared" si="0"/>
@@ -6948,9 +7489,12 @@
         <f t="shared" ref="K38" si="14">J38*5</f>
         <v>10</v>
       </c>
-      <c r="L38" s="27"/>
-    </row>
-    <row r="39" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L38" s="68">
+        <v>1.4220000000000002</v>
+      </c>
+      <c r="M38" s="27"/>
+    </row>
+    <row r="39" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A39" s="44"/>
       <c r="B39" s="39">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -6984,9 +7528,12 @@
         <f>J39*5</f>
         <v>15</v>
       </c>
-      <c r="L39" s="28"/>
-    </row>
-    <row r="40" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L39" s="68">
+        <v>1.492</v>
+      </c>
+      <c r="M39" s="28"/>
+    </row>
+    <row r="40" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44"/>
       <c r="B40" s="41">
         <f t="shared" si="0"/>
@@ -7020,9 +7567,12 @@
         <f t="shared" ref="K40" si="15">J40*5</f>
         <v>10</v>
       </c>
-      <c r="L40" s="27"/>
-    </row>
-    <row r="41" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L40" s="68">
+        <v>1.33</v>
+      </c>
+      <c r="M40" s="27"/>
+    </row>
+    <row r="41" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="44"/>
       <c r="B41" s="39">
         <f>ROW(B41) - ROW($B$9)</f>
@@ -7056,9 +7606,12 @@
         <f>J41*5</f>
         <v>15</v>
       </c>
-      <c r="L41" s="28"/>
-    </row>
-    <row r="42" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L41" s="68">
+        <v>1.516</v>
+      </c>
+      <c r="M41" s="28"/>
+    </row>
+    <row r="42" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="44"/>
       <c r="B42" s="41">
         <f t="shared" si="0"/>
@@ -7090,9 +7643,12 @@
         <f t="shared" ref="K42" si="16">J42*5</f>
         <v>15</v>
       </c>
-      <c r="L42" s="27"/>
-    </row>
-    <row r="43" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L42" s="68">
+        <v>0.99</v>
+      </c>
+      <c r="M42" s="27"/>
+    </row>
+    <row r="43" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
       <c r="B43" s="39">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -7126,9 +7682,12 @@
         <f>J43*5</f>
         <v>10</v>
       </c>
-      <c r="L43" s="28"/>
-    </row>
-    <row r="44" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L43" s="68">
+        <v>1.04</v>
+      </c>
+      <c r="M43" s="28"/>
+    </row>
+    <row r="44" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A44" s="44"/>
       <c r="B44" s="41">
         <f t="shared" si="0"/>
@@ -7162,9 +7721,12 @@
         <f t="shared" ref="K44" si="17">J44*5</f>
         <v>15</v>
       </c>
-      <c r="L44" s="27"/>
-    </row>
-    <row r="45" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L44" s="68">
+        <v>1.464</v>
+      </c>
+      <c r="M44" s="27"/>
+    </row>
+    <row r="45" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="44"/>
       <c r="B45" s="39">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -7198,9 +7760,12 @@
         <f>J45*5</f>
         <v>10</v>
       </c>
-      <c r="L45" s="28"/>
-    </row>
-    <row r="46" spans="1:12" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="L45" s="68">
+        <v>1.4180000000000001</v>
+      </c>
+      <c r="M45" s="28"/>
+    </row>
+    <row r="46" spans="1:13" s="45" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
       <c r="B46" s="41">
         <f t="shared" si="0"/>
@@ -7234,9 +7799,12 @@
         <f t="shared" ref="K46" si="18">J46*5</f>
         <v>15</v>
       </c>
-      <c r="L46" s="27"/>
-    </row>
-    <row r="47" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L46" s="68">
+        <v>1.524</v>
+      </c>
+      <c r="M46" s="27"/>
+    </row>
+    <row r="47" spans="1:13" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="44"/>
       <c r="B47" s="39">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -7270,9 +7838,12 @@
         <f>J47*5</f>
         <v>10</v>
       </c>
-      <c r="L47" s="28"/>
-    </row>
-    <row r="48" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L47" s="68">
+        <v>1.476</v>
+      </c>
+      <c r="M47" s="28"/>
+    </row>
+    <row r="48" spans="1:13" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A48" s="44"/>
       <c r="B48" s="41">
         <f t="shared" si="0"/>
@@ -7306,9 +7877,12 @@
         <f t="shared" ref="K48" si="19">J48*5</f>
         <v>10</v>
       </c>
-      <c r="L48" s="27"/>
-    </row>
-    <row r="49" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L48" s="68">
+        <v>1.5680000000000001</v>
+      </c>
+      <c r="M48" s="27"/>
+    </row>
+    <row r="49" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
       <c r="B49" s="39">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -7342,9 +7916,12 @@
         <f>J49*5</f>
         <v>15</v>
       </c>
-      <c r="L49" s="28"/>
-    </row>
-    <row r="50" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L49" s="68">
+        <v>1.4359999999999999</v>
+      </c>
+      <c r="M49" s="28"/>
+    </row>
+    <row r="50" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="44"/>
       <c r="B50" s="41">
         <f t="shared" si="0"/>
@@ -7378,9 +7955,12 @@
         <f t="shared" ref="K50" si="20">J50*5</f>
         <v>5</v>
       </c>
-      <c r="L50" s="27"/>
-    </row>
-    <row r="51" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L50" s="68">
+        <v>1.508</v>
+      </c>
+      <c r="M50" s="27"/>
+    </row>
+    <row r="51" spans="1:18" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A51" s="44"/>
       <c r="B51" s="39">
         <f>ROW(B51) - ROW($B$9)</f>
@@ -7414,9 +7994,12 @@
         <f>J51*5</f>
         <v>5</v>
       </c>
-      <c r="L51" s="28"/>
-    </row>
-    <row r="52" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L51" s="68">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="M51" s="28"/>
+    </row>
+    <row r="52" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A52" s="44"/>
       <c r="B52" s="41">
         <f t="shared" si="0"/>
@@ -7450,9 +8033,12 @@
         <f t="shared" ref="K52" si="21">J52*5</f>
         <v>5</v>
       </c>
-      <c r="L52" s="27"/>
-    </row>
-    <row r="53" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L52" s="68">
+        <v>1.6920000000000002</v>
+      </c>
+      <c r="M52" s="27"/>
+    </row>
+    <row r="53" spans="1:18" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A53" s="44"/>
       <c r="B53" s="39">
         <f>ROW(B53) - ROW($B$9)</f>
@@ -7486,9 +8072,12 @@
         <f>J53*5</f>
         <v>5</v>
       </c>
-      <c r="L53" s="28"/>
-    </row>
-    <row r="54" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L53" s="68">
+        <v>1.3540000000000001</v>
+      </c>
+      <c r="M53" s="28"/>
+    </row>
+    <row r="54" spans="1:18" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A54" s="44"/>
       <c r="B54" s="41">
         <f t="shared" si="0"/>
@@ -7522,9 +8111,13 @@
         <f t="shared" ref="K54" si="22">J54*5</f>
         <v>5</v>
       </c>
-      <c r="L54" s="27"/>
-    </row>
-    <row r="55" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L54" s="68">
+        <v>1.544</v>
+      </c>
+      <c r="M54" s="27"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A55" s="44"/>
       <c r="B55" s="39">
         <f>ROW(B55) - ROW($B$9)</f>
@@ -7558,9 +8151,12 @@
         <f>J55*5</f>
         <v>5</v>
       </c>
-      <c r="L55" s="28"/>
-    </row>
-    <row r="56" spans="1:12" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="L55" s="68">
+        <v>1.4239999999999999</v>
+      </c>
+      <c r="M55" s="28"/>
+    </row>
+    <row r="56" spans="1:18" s="45" customFormat="1" ht="48" x14ac:dyDescent="0.25">
       <c r="A56" s="44"/>
       <c r="B56" s="41">
         <f t="shared" si="0"/>
@@ -7594,9 +8190,12 @@
         <f t="shared" ref="K56:K57" si="23">J56*5</f>
         <v>5</v>
       </c>
-      <c r="L56" s="27"/>
-    </row>
-    <row r="57" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L56" s="68">
+        <v>1.3940000000000001</v>
+      </c>
+      <c r="M56" s="27"/>
+    </row>
+    <row r="57" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
       <c r="B57" s="41">
         <f t="shared" si="0"/>
@@ -7630,9 +8229,12 @@
         <f t="shared" si="23"/>
         <v>5</v>
       </c>
-      <c r="L57" s="28"/>
-    </row>
-    <row r="58" spans="1:12" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="L57" s="69">
+        <v>2.36</v>
+      </c>
+      <c r="M57" s="28"/>
+    </row>
+    <row r="58" spans="1:18" s="45" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A58" s="44"/>
       <c r="B58" s="39">
         <f>ROW(B58) - ROW($B$9)</f>
@@ -7666,9 +8268,12 @@
         <f>J58*5</f>
         <v>10</v>
       </c>
-      <c r="L58" s="27"/>
-    </row>
-    <row r="59" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L58" s="68">
+        <v>1.4279999999999999</v>
+      </c>
+      <c r="M58" s="27"/>
+    </row>
+    <row r="59" spans="1:18" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="44"/>
       <c r="B59" s="41">
         <f t="shared" si="0"/>
@@ -7702,9 +8307,12 @@
         <f t="shared" ref="K59" si="24">J59*5</f>
         <v>10</v>
       </c>
-      <c r="L59" s="28"/>
-    </row>
-    <row r="60" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="L59" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="M59" s="28"/>
+    </row>
+    <row r="60" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="39">
         <f>ROW(B60) - ROW($B$9)</f>
@@ -7738,9 +8346,13 @@
         <f>J60*5</f>
         <v>45</v>
       </c>
-      <c r="L60" s="28"/>
-    </row>
-    <row r="61" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L60" s="68">
+        <v>22.756200000000003</v>
+      </c>
+      <c r="M60" s="28"/>
+      <c r="R60" s="45"/>
+    </row>
+    <row r="61" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="49">
         <f t="shared" si="0"/>
@@ -7774,9 +8386,13 @@
         <f t="shared" ref="K61" si="25">J61*5</f>
         <v>15</v>
       </c>
-      <c r="L61" s="51"/>
-    </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L61" s="71">
+        <v>3.198</v>
+      </c>
+      <c r="M61" s="51"/>
+      <c r="R61" s="45"/>
+    </row>
+    <row r="62" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="52"/>
       <c r="C62" s="53"/>
       <c r="D62" s="54"/>
@@ -7784,17 +8400,39 @@
       <c r="F62" s="56"/>
       <c r="G62" s="57"/>
       <c r="H62" s="56"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
-      <c r="L62" s="64"/>
+      <c r="I62" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="J62" s="73"/>
+      <c r="K62" s="73"/>
+      <c r="L62" s="74">
+        <f>SUM(L10:L61)</f>
+        <v>112.68010000000001</v>
+      </c>
+      <c r="M62" s="64"/>
+      <c r="R62" s="45"/>
+    </row>
+    <row r="63" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="72" t="s">
+        <v>260</v>
+      </c>
+      <c r="J63" s="73"/>
+      <c r="K63" s="73"/>
+      <c r="L63" s="75">
+        <f>L62/5</f>
+        <v>22.536020000000001</v>
+      </c>
+      <c r="R63" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="L3:L8"/>
+  <mergeCells count="4">
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 Board" sheetId="1" r:id="rId1"/>
@@ -1389,15 +1389,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1410,14 +1401,6 @@
     <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="14" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1429,6 +1412,23 @@
     </xf>
     <xf numFmtId="165" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1904,10 +1904,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1943,7 +1943,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="66"/>
+      <c r="L3" s="74"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1961,7 +1961,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="46"/>
-      <c r="L4" s="67"/>
+      <c r="L4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1979,7 +1979,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="46"/>
-      <c r="L5" s="67"/>
+      <c r="L5" s="75"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1993,7 +1993,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="46"/>
-      <c r="L6" s="67"/>
+      <c r="L6" s="75"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2007,7 +2007,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="67"/>
+      <c r="L7" s="75"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2021,7 +2021,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="67"/>
+      <c r="L8" s="75"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2089,8 +2089,8 @@
       <c r="J10" s="27">
         <v>4</v>
       </c>
-      <c r="K10" s="68">
-        <v>1.2999999999999998</v>
+      <c r="K10" s="65">
+        <v>0.65</v>
       </c>
       <c r="L10" s="27"/>
     </row>
@@ -2124,8 +2124,8 @@
       <c r="J11" s="28">
         <v>4</v>
       </c>
-      <c r="K11" s="69">
-        <v>1.278</v>
+      <c r="K11" s="66">
+        <v>0.7</v>
       </c>
       <c r="L11" s="28"/>
     </row>
@@ -2159,8 +2159,8 @@
       <c r="J12" s="27">
         <v>1</v>
       </c>
-      <c r="K12" s="68">
-        <v>1.125</v>
+      <c r="K12" s="65">
+        <v>0.3</v>
       </c>
       <c r="L12" s="27"/>
     </row>
@@ -2194,8 +2194,8 @@
       <c r="J13" s="28">
         <v>1</v>
       </c>
-      <c r="K13" s="69">
-        <v>1</v>
+      <c r="K13" s="66">
+        <v>0.3</v>
       </c>
       <c r="L13" s="28"/>
     </row>
@@ -2229,8 +2229,8 @@
       <c r="J14" s="27">
         <v>1</v>
       </c>
-      <c r="K14" s="68">
-        <v>1.1339999999999999</v>
+      <c r="K14" s="65">
+        <v>0.3</v>
       </c>
       <c r="L14" s="27"/>
     </row>
@@ -2264,7 +2264,7 @@
       <c r="J15" s="28">
         <v>2</v>
       </c>
-      <c r="K15" s="69">
+      <c r="K15" s="66">
         <v>1.258</v>
       </c>
       <c r="L15" s="28"/>
@@ -2299,8 +2299,8 @@
       <c r="J16" s="27">
         <v>1</v>
       </c>
-      <c r="K16" s="68">
-        <v>1.1499999999999999</v>
+      <c r="K16" s="65">
+        <v>0.35</v>
       </c>
       <c r="L16" s="27"/>
     </row>
@@ -2334,8 +2334,8 @@
       <c r="J17" s="28">
         <v>1</v>
       </c>
-      <c r="K17" s="69">
-        <v>1.1599999999999999</v>
+      <c r="K17" s="66">
+        <v>0.25</v>
       </c>
       <c r="L17" s="28"/>
     </row>
@@ -2369,8 +2369,8 @@
       <c r="J18" s="27">
         <v>1</v>
       </c>
-      <c r="K18" s="68">
-        <v>1.08</v>
+      <c r="K18" s="65">
+        <v>0.25</v>
       </c>
       <c r="L18" s="27"/>
     </row>
@@ -2404,8 +2404,8 @@
       <c r="J19" s="28">
         <v>2</v>
       </c>
-      <c r="K19" s="69">
-        <v>1.9411</v>
+      <c r="K19" s="66">
+        <v>0.4</v>
       </c>
       <c r="L19" s="28"/>
     </row>
@@ -2439,8 +2439,8 @@
       <c r="J20" s="27">
         <v>1</v>
       </c>
-      <c r="K20" s="68">
-        <v>1.345</v>
+      <c r="K20" s="65">
+        <v>0.25</v>
       </c>
       <c r="L20" s="27"/>
     </row>
@@ -2474,8 +2474,8 @@
       <c r="J21" s="28">
         <v>1</v>
       </c>
-      <c r="K21" s="69">
-        <v>1.3363999999999998</v>
+      <c r="K21" s="66">
+        <v>0.3</v>
       </c>
       <c r="L21" s="28"/>
     </row>
@@ -2509,8 +2509,8 @@
       <c r="J22" s="27">
         <v>1</v>
       </c>
-      <c r="K22" s="68">
-        <v>0.95499999999999996</v>
+      <c r="K22" s="65">
+        <v>0.2</v>
       </c>
       <c r="L22" s="27"/>
     </row>
@@ -2544,8 +2544,8 @@
       <c r="J23" s="28">
         <v>1</v>
       </c>
-      <c r="K23" s="69">
-        <v>1.3919999999999999</v>
+      <c r="K23" s="66">
+        <v>0.35</v>
       </c>
       <c r="L23" s="28"/>
     </row>
@@ -2579,8 +2579,8 @@
       <c r="J24" s="27">
         <v>1</v>
       </c>
-      <c r="K24" s="68">
-        <v>1.1179999999999999</v>
+      <c r="K24" s="65">
+        <v>0.3</v>
       </c>
       <c r="L24" s="27"/>
     </row>
@@ -2614,8 +2614,8 @@
       <c r="J25" s="28">
         <v>1</v>
       </c>
-      <c r="K25" s="69">
-        <v>1.4049999999999998</v>
+      <c r="K25" s="66">
+        <v>0.35</v>
       </c>
       <c r="L25" s="28"/>
     </row>
@@ -2649,8 +2649,8 @@
       <c r="J26" s="27">
         <v>1</v>
       </c>
-      <c r="K26" s="68">
-        <v>1.0549999999999999</v>
+      <c r="K26" s="65">
+        <v>1.72</v>
       </c>
       <c r="L26" s="27"/>
     </row>
@@ -2684,8 +2684,8 @@
       <c r="J27" s="28">
         <v>2</v>
       </c>
-      <c r="K27" s="69">
-        <v>2.2290000000000001</v>
+      <c r="K27" s="66">
+        <v>2.58</v>
       </c>
       <c r="L27" s="28"/>
     </row>
@@ -2719,8 +2719,8 @@
       <c r="J28" s="27">
         <v>13</v>
       </c>
-      <c r="K28" s="68">
-        <v>1.1459999999999999</v>
+      <c r="K28" s="65">
+        <v>0.88</v>
       </c>
       <c r="L28" s="27"/>
     </row>
@@ -2754,8 +2754,8 @@
       <c r="J29" s="28">
         <v>1</v>
       </c>
-      <c r="K29" s="69">
-        <v>1.4550000000000001</v>
+      <c r="K29" s="66">
+        <v>0.72</v>
       </c>
       <c r="L29" s="28"/>
     </row>
@@ -2789,8 +2789,8 @@
       <c r="J30" s="27">
         <v>4</v>
       </c>
-      <c r="K30" s="68">
-        <v>1.1499999999999999</v>
+      <c r="K30" s="65">
+        <v>0.47</v>
       </c>
       <c r="L30" s="27"/>
     </row>
@@ -2824,8 +2824,8 @@
       <c r="J31" s="28">
         <v>2</v>
       </c>
-      <c r="K31" s="69">
-        <v>1.2999999999999998</v>
+      <c r="K31" s="66">
+        <v>0.4</v>
       </c>
       <c r="L31" s="28"/>
     </row>
@@ -2859,8 +2859,8 @@
       <c r="J32" s="27">
         <v>1</v>
       </c>
-      <c r="K32" s="68">
-        <v>1.268</v>
+      <c r="K32" s="65">
+        <v>0.25</v>
       </c>
       <c r="L32" s="27"/>
     </row>
@@ -2894,7 +2894,7 @@
       <c r="J33" s="28">
         <v>1</v>
       </c>
-      <c r="K33" s="69">
+      <c r="K33" s="66">
         <v>2.4249999999999998</v>
       </c>
       <c r="L33" s="28"/>
@@ -2929,8 +2929,8 @@
       <c r="J34" s="28">
         <v>2</v>
       </c>
-      <c r="K34" s="68">
-        <v>1.292</v>
+      <c r="K34" s="65">
+        <v>0.45</v>
       </c>
       <c r="L34" s="27"/>
     </row>
@@ -2964,8 +2964,8 @@
       <c r="J35" s="27">
         <v>1</v>
       </c>
-      <c r="K35" s="68">
-        <v>1.2439999999999998</v>
+      <c r="K35" s="65">
+        <v>0.3</v>
       </c>
       <c r="L35" s="28"/>
     </row>
@@ -2999,8 +2999,8 @@
       <c r="J36" s="28">
         <v>2</v>
       </c>
-      <c r="K36" s="68">
-        <v>1.115</v>
+      <c r="K36" s="65">
+        <v>0.38</v>
       </c>
       <c r="L36" s="27"/>
     </row>
@@ -3034,8 +3034,8 @@
       <c r="J37" s="27">
         <v>3</v>
       </c>
-      <c r="K37" s="68">
-        <v>1.1299999999999999</v>
+      <c r="K37" s="65">
+        <v>0.57999999999999996</v>
       </c>
       <c r="L37" s="28"/>
     </row>
@@ -3069,8 +3069,8 @@
       <c r="J38" s="28">
         <v>2</v>
       </c>
-      <c r="K38" s="68">
-        <v>1.202</v>
+      <c r="K38" s="65">
+        <v>0.6</v>
       </c>
       <c r="L38" s="27"/>
     </row>
@@ -3104,8 +3104,8 @@
       <c r="J39" s="27">
         <v>3</v>
       </c>
-      <c r="K39" s="68">
-        <v>1.272</v>
+      <c r="K39" s="65">
+        <v>0.7</v>
       </c>
       <c r="L39" s="28"/>
     </row>
@@ -3139,8 +3139,8 @@
       <c r="J40" s="28">
         <v>2</v>
       </c>
-      <c r="K40" s="68">
-        <v>1.1099999999999999</v>
+      <c r="K40" s="65">
+        <v>0.37</v>
       </c>
       <c r="L40" s="27"/>
     </row>
@@ -3174,8 +3174,8 @@
       <c r="J41" s="27">
         <v>3</v>
       </c>
-      <c r="K41" s="68">
-        <v>1.2959999999999998</v>
+      <c r="K41" s="65">
+        <v>0.49</v>
       </c>
       <c r="L41" s="28"/>
     </row>
@@ -3207,8 +3207,8 @@
       <c r="J42" s="28">
         <v>3</v>
       </c>
-      <c r="K42" s="68">
-        <v>0.76999999999999991</v>
+      <c r="K42" s="65">
+        <v>0.7</v>
       </c>
       <c r="L42" s="27"/>
     </row>
@@ -3242,8 +3242,8 @@
       <c r="J43" s="27">
         <v>2</v>
       </c>
-      <c r="K43" s="68">
-        <v>0.82</v>
+      <c r="K43" s="65">
+        <v>0.25</v>
       </c>
       <c r="L43" s="28"/>
     </row>
@@ -3277,8 +3277,8 @@
       <c r="J44" s="28">
         <v>3</v>
       </c>
-      <c r="K44" s="68">
-        <v>1.2439999999999998</v>
+      <c r="K44" s="65">
+        <v>0.45</v>
       </c>
       <c r="L44" s="27"/>
     </row>
@@ -3312,8 +3312,8 @@
       <c r="J45" s="27">
         <v>2</v>
       </c>
-      <c r="K45" s="68">
-        <v>1.198</v>
+      <c r="K45" s="65">
+        <v>0.36</v>
       </c>
       <c r="L45" s="28"/>
     </row>
@@ -3347,8 +3347,8 @@
       <c r="J46" s="28">
         <v>3</v>
       </c>
-      <c r="K46" s="68">
-        <v>1.3039999999999998</v>
+      <c r="K46" s="65">
+        <v>0.9</v>
       </c>
       <c r="L46" s="27"/>
     </row>
@@ -3382,8 +3382,8 @@
       <c r="J47" s="27">
         <v>2</v>
       </c>
-      <c r="K47" s="68">
-        <v>1.2559999999999998</v>
+      <c r="K47" s="65">
+        <v>0.55000000000000004</v>
       </c>
       <c r="L47" s="28"/>
     </row>
@@ -3417,8 +3417,8 @@
       <c r="J48" s="28">
         <v>2</v>
       </c>
-      <c r="K48" s="68">
-        <v>1.3479999999999999</v>
+      <c r="K48" s="65">
+        <v>0.65</v>
       </c>
       <c r="L48" s="27"/>
     </row>
@@ -3452,8 +3452,8 @@
       <c r="J49" s="27">
         <v>3</v>
       </c>
-      <c r="K49" s="68">
-        <v>1.216</v>
+      <c r="K49" s="65">
+        <v>0.85</v>
       </c>
       <c r="L49" s="28"/>
     </row>
@@ -3487,8 +3487,8 @@
       <c r="J50" s="28">
         <v>1</v>
       </c>
-      <c r="K50" s="68">
-        <v>1.2879999999999998</v>
+      <c r="K50" s="65">
+        <v>0.2</v>
       </c>
       <c r="L50" s="27"/>
     </row>
@@ -3522,8 +3522,8 @@
       <c r="J51" s="27">
         <v>1</v>
       </c>
-      <c r="K51" s="68">
-        <v>0.8899999999999999</v>
+      <c r="K51" s="65">
+        <v>0.4</v>
       </c>
       <c r="L51" s="28"/>
     </row>
@@ -3557,8 +3557,8 @@
       <c r="J52" s="28">
         <v>1</v>
       </c>
-      <c r="K52" s="68">
-        <v>1.472</v>
+      <c r="K52" s="65">
+        <v>0.3</v>
       </c>
       <c r="L52" s="27"/>
     </row>
@@ -3592,8 +3592,8 @@
       <c r="J53" s="27">
         <v>1</v>
       </c>
-      <c r="K53" s="68">
-        <v>1.1339999999999999</v>
+      <c r="K53" s="65">
+        <v>0.25</v>
       </c>
       <c r="L53" s="28"/>
     </row>
@@ -3627,8 +3627,8 @@
       <c r="J54" s="28">
         <v>1</v>
       </c>
-      <c r="K54" s="68">
-        <v>1.3239999999999998</v>
+      <c r="K54" s="65">
+        <v>0.25</v>
       </c>
       <c r="L54" s="27"/>
     </row>
@@ -3662,8 +3662,8 @@
       <c r="J55" s="27">
         <v>1</v>
       </c>
-      <c r="K55" s="68">
-        <v>1.204</v>
+      <c r="K55" s="65">
+        <v>0.25</v>
       </c>
       <c r="L55" s="28"/>
     </row>
@@ -3697,8 +3697,8 @@
       <c r="J56" s="28">
         <v>1</v>
       </c>
-      <c r="K56" s="68">
-        <v>1.1739999999999999</v>
+      <c r="K56" s="65">
+        <v>0.25</v>
       </c>
       <c r="L56" s="27"/>
     </row>
@@ -3732,8 +3732,8 @@
       <c r="J57" s="28">
         <v>1</v>
       </c>
-      <c r="K57" s="69">
-        <v>1.42</v>
+      <c r="K57" s="66">
+        <v>0.8</v>
       </c>
       <c r="L57" s="28"/>
     </row>
@@ -3767,8 +3767,8 @@
       <c r="J58" s="27">
         <v>2</v>
       </c>
-      <c r="K58" s="68">
-        <v>1.208</v>
+      <c r="K58" s="65">
+        <v>0.42</v>
       </c>
       <c r="L58" s="27"/>
     </row>
@@ -3802,7 +3802,7 @@
       <c r="J59" s="43">
         <v>2</v>
       </c>
-      <c r="K59" s="76" t="s">
+      <c r="K59" s="71" t="s">
         <v>236</v>
       </c>
       <c r="L59" s="27"/>
@@ -3837,8 +3837,8 @@
       <c r="J60" s="27">
         <v>9</v>
       </c>
-      <c r="K60" s="68">
-        <v>11.042</v>
+      <c r="K60" s="65">
+        <v>13.6</v>
       </c>
       <c r="L60" s="27"/>
     </row>
@@ -3872,8 +3872,8 @@
       <c r="J61" s="51">
         <v>3</v>
       </c>
-      <c r="K61" s="77">
-        <v>1.839</v>
+      <c r="K61" s="72">
+        <v>3.8</v>
       </c>
       <c r="L61" s="27"/>
     </row>
@@ -3884,14 +3884,14 @@
       <c r="E62" s="55"/>
       <c r="F62" s="56"/>
       <c r="G62" s="57"/>
-      <c r="H62" s="72" t="s">
+      <c r="H62" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="I62" s="73"/>
-      <c r="J62" s="73"/>
-      <c r="K62" s="74">
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="69">
         <f>SUM(K10:K61)</f>
-        <v>74.817499999999995</v>
+        <v>45.052999999999997</v>
       </c>
       <c r="L62" s="57"/>
     </row>
@@ -3935,11 +3935,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3977,7 +3977,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="66"/>
+      <c r="M3" s="74"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3996,7 +3996,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="46"/>
       <c r="L4" s="46"/>
-      <c r="M4" s="67"/>
+      <c r="M4" s="75"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4015,7 +4015,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="46"/>
       <c r="L5" s="46"/>
-      <c r="M5" s="67"/>
+      <c r="M5" s="75"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4030,7 +4030,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="46"/>
       <c r="L6" s="46"/>
-      <c r="M6" s="67"/>
+      <c r="M6" s="75"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4045,7 +4045,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="67"/>
+      <c r="M7" s="75"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4060,7 +4060,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="67"/>
+      <c r="M8" s="75"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4135,8 +4135,8 @@
         <f>J10*2</f>
         <v>8</v>
       </c>
-      <c r="L10" s="68">
-        <v>1.35</v>
+      <c r="L10" s="65">
+        <v>0.8</v>
       </c>
       <c r="M10" s="27"/>
     </row>
@@ -4174,8 +4174,8 @@
         <f t="shared" ref="K11:K61" si="1">J11*2</f>
         <v>8</v>
       </c>
-      <c r="L11" s="68">
-        <v>1.3279999999999998</v>
+      <c r="L11" s="66">
+        <v>0.75</v>
       </c>
       <c r="M11" s="28"/>
     </row>
@@ -4213,8 +4213,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L12" s="68">
-        <v>1.175</v>
+      <c r="L12" s="65">
+        <v>0.3</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -4252,8 +4252,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L13" s="68">
-        <v>1.05</v>
+      <c r="L13" s="66">
+        <v>0.3</v>
       </c>
       <c r="M13" s="28"/>
     </row>
@@ -4291,8 +4291,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L14" s="68">
-        <v>1.1839999999999999</v>
+      <c r="L14" s="65">
+        <v>0.3</v>
       </c>
       <c r="M14" s="27"/>
     </row>
@@ -4330,8 +4330,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L15" s="68">
-        <v>1.3080000000000001</v>
+      <c r="L15" s="66">
+        <v>2.4500000000000002</v>
       </c>
       <c r="M15" s="28"/>
     </row>
@@ -4369,8 +4369,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L16" s="68">
-        <v>1.2</v>
+      <c r="L16" s="65">
+        <v>0.35</v>
       </c>
       <c r="M16" s="27"/>
     </row>
@@ -4408,8 +4408,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L17" s="68">
-        <v>1.21</v>
+      <c r="L17" s="66">
+        <v>0.35</v>
       </c>
       <c r="M17" s="28"/>
     </row>
@@ -4447,8 +4447,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L18" s="68">
-        <v>1.1299999999999999</v>
+      <c r="L18" s="65">
+        <v>0.35</v>
       </c>
       <c r="M18" s="27"/>
     </row>
@@ -4486,8 +4486,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L19" s="68">
-        <v>2.8185000000000002</v>
+      <c r="L19" s="66">
+        <v>0.65</v>
       </c>
       <c r="M19" s="28"/>
     </row>
@@ -4525,8 +4525,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L20" s="68">
-        <v>1.395</v>
+      <c r="L20" s="65">
+        <v>0.25</v>
       </c>
       <c r="M20" s="27"/>
     </row>
@@ -4564,8 +4564,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L21" s="68">
-        <v>1.7045999999999999</v>
+      <c r="L21" s="66">
+        <v>0.3</v>
       </c>
       <c r="M21" s="28"/>
     </row>
@@ -4603,8 +4603,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L22" s="68">
-        <v>1.0049999999999999</v>
+      <c r="L22" s="65">
+        <v>0.3</v>
       </c>
       <c r="M22" s="27"/>
     </row>
@@ -4642,8 +4642,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L23" s="68">
-        <v>1.4419999999999999</v>
+      <c r="L23" s="66">
+        <v>0.4</v>
       </c>
       <c r="M23" s="28"/>
     </row>
@@ -4681,8 +4681,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L24" s="68">
-        <v>1.1679999999999999</v>
+      <c r="L24" s="65">
+        <v>0.48</v>
       </c>
       <c r="M24" s="27"/>
     </row>
@@ -4720,8 +4720,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L25" s="68">
-        <v>1.4550000000000001</v>
+      <c r="L25" s="66">
+        <v>0.52</v>
       </c>
       <c r="M25" s="28"/>
     </row>
@@ -4759,8 +4759,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L26" s="68">
-        <v>1.2825</v>
+      <c r="L26" s="65">
+        <v>2.3199999999999998</v>
       </c>
       <c r="M26" s="27"/>
     </row>
@@ -4798,8 +4798,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L27" s="68">
-        <v>2.2789999999999999</v>
+      <c r="L27" s="65">
+        <v>3.8</v>
       </c>
       <c r="M27" s="28"/>
     </row>
@@ -4837,8 +4837,8 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="L28" s="68">
-        <v>1.6419999999999999</v>
+      <c r="L28" s="65">
+        <v>1.2</v>
       </c>
       <c r="M28" s="27"/>
     </row>
@@ -4876,8 +4876,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L29" s="68">
-        <v>1.5049999999999999</v>
+      <c r="L29" s="65">
+        <v>0.35</v>
       </c>
       <c r="M29" s="28"/>
     </row>
@@ -4915,8 +4915,8 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="L30" s="68">
-        <v>1.2</v>
+      <c r="L30" s="65">
+        <v>0.65</v>
       </c>
       <c r="M30" s="27"/>
     </row>
@@ -4954,8 +4954,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L31" s="68">
-        <v>1.35</v>
+      <c r="L31" s="65">
+        <v>0.42</v>
       </c>
       <c r="M31" s="28"/>
     </row>
@@ -4993,8 +4993,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L32" s="68">
-        <v>1.3180000000000001</v>
+      <c r="L32" s="65">
+        <v>0.4</v>
       </c>
       <c r="M32" s="27"/>
     </row>
@@ -5032,8 +5032,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L33" s="68">
-        <v>2.4749999999999996</v>
+      <c r="L33" s="65">
+        <v>3.76</v>
       </c>
       <c r="M33" s="28"/>
     </row>
@@ -5071,8 +5071,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L34" s="68">
-        <v>1.3420000000000001</v>
+      <c r="L34" s="65">
+        <v>0.7</v>
       </c>
       <c r="M34" s="27"/>
     </row>
@@ -5110,8 +5110,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L35" s="68">
-        <v>1.294</v>
+      <c r="L35" s="65">
+        <v>0.48</v>
       </c>
       <c r="M35" s="28"/>
     </row>
@@ -5149,8 +5149,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L36" s="68">
-        <v>1.165</v>
+      <c r="L36" s="65">
+        <v>0.9</v>
       </c>
       <c r="M36" s="27"/>
     </row>
@@ -5188,8 +5188,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L37" s="68">
-        <v>1.18</v>
+      <c r="L37" s="65">
+        <v>0.75</v>
       </c>
       <c r="M37" s="28"/>
     </row>
@@ -5227,8 +5227,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L38" s="68">
-        <v>1.252</v>
+      <c r="L38" s="65">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M38" s="27"/>
     </row>
@@ -5266,8 +5266,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L39" s="68">
-        <v>1.3220000000000001</v>
+      <c r="L39" s="65">
+        <v>0.67</v>
       </c>
       <c r="M39" s="28"/>
     </row>
@@ -5305,8 +5305,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L40" s="68">
-        <v>1.1600000000000001</v>
+      <c r="L40" s="65">
+        <v>0.38</v>
       </c>
       <c r="M40" s="27"/>
     </row>
@@ -5344,8 +5344,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L41" s="68">
-        <v>1.3460000000000001</v>
+      <c r="L41" s="65">
+        <v>0.78</v>
       </c>
       <c r="M41" s="28"/>
     </row>
@@ -5381,8 +5381,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L42" s="68">
-        <v>0.82</v>
+      <c r="L42" s="65">
+        <v>0.69</v>
       </c>
       <c r="M42" s="27"/>
     </row>
@@ -5420,8 +5420,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L43" s="68">
-        <v>0.87</v>
+      <c r="L43" s="65">
+        <v>0.6</v>
       </c>
       <c r="M43" s="28"/>
     </row>
@@ -5459,8 +5459,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L44" s="68">
-        <v>1.294</v>
+      <c r="L44" s="65">
+        <v>0.7</v>
       </c>
       <c r="M44" s="27"/>
     </row>
@@ -5498,8 +5498,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L45" s="68">
-        <v>1.248</v>
+      <c r="L45" s="65">
+        <v>0.45</v>
       </c>
       <c r="M45" s="28"/>
     </row>
@@ -5537,8 +5537,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L46" s="68">
-        <v>1.3540000000000001</v>
+      <c r="L46" s="65">
+        <v>0.5</v>
       </c>
       <c r="M46" s="27"/>
     </row>
@@ -5576,8 +5576,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L47" s="68">
-        <v>1.306</v>
+      <c r="L47" s="65">
+        <v>0.47</v>
       </c>
       <c r="M47" s="28"/>
     </row>
@@ -5615,8 +5615,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L48" s="68">
-        <v>1.3979999999999999</v>
+      <c r="L48" s="65">
+        <v>0.6</v>
       </c>
       <c r="M48" s="27"/>
     </row>
@@ -5654,8 +5654,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L49" s="68">
-        <v>1.266</v>
+      <c r="L49" s="65">
+        <v>0.8</v>
       </c>
       <c r="M49" s="28"/>
     </row>
@@ -5693,8 +5693,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L50" s="68">
-        <v>1.3380000000000001</v>
+      <c r="L50" s="65">
+        <v>0.45</v>
       </c>
       <c r="M50" s="27"/>
     </row>
@@ -5732,8 +5732,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L51" s="68">
-        <v>0.94</v>
+      <c r="L51" s="65">
+        <v>0.37</v>
       </c>
       <c r="M51" s="28"/>
     </row>
@@ -5771,8 +5771,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L52" s="68">
-        <v>1.522</v>
+      <c r="L52" s="65">
+        <v>0.4</v>
       </c>
       <c r="M52" s="27"/>
     </row>
@@ -5810,8 +5810,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L53" s="68">
-        <v>1.1839999999999999</v>
+      <c r="L53" s="65">
+        <v>0.33</v>
       </c>
       <c r="M53" s="28"/>
     </row>
@@ -5849,8 +5849,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L54" s="68">
-        <v>1.3740000000000001</v>
+      <c r="L54" s="65">
+        <v>0.3</v>
       </c>
       <c r="M54" s="27"/>
     </row>
@@ -5888,8 +5888,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L55" s="68">
-        <v>1.254</v>
+      <c r="L55" s="65">
+        <v>0.25</v>
       </c>
       <c r="M55" s="28"/>
     </row>
@@ -5927,8 +5927,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L56" s="68">
-        <v>1.224</v>
+      <c r="L56" s="65">
+        <v>0.44</v>
       </c>
       <c r="M56" s="27"/>
     </row>
@@ -5966,8 +5966,8 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L57" s="68">
-        <v>1.47</v>
+      <c r="L57" s="65">
+        <v>0.13</v>
       </c>
       <c r="M57" s="28"/>
     </row>
@@ -6005,8 +6005,8 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L58" s="68">
-        <v>1.258</v>
+      <c r="L58" s="65">
+        <v>0.45</v>
       </c>
       <c r="M58" s="27"/>
     </row>
@@ -6044,7 +6044,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L59" s="68" t="s">
+      <c r="L59" s="65" t="s">
         <v>236</v>
       </c>
       <c r="M59" s="28"/>
@@ -6083,8 +6083,8 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="L60" s="68">
-        <v>11.092000000000001</v>
+      <c r="L60" s="65">
+        <v>15.7</v>
       </c>
       <c r="M60" s="28"/>
       <c r="Q60" s="45"/>
@@ -6123,8 +6123,8 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L61" s="68">
-        <v>1.889</v>
+      <c r="L61" s="65">
+        <v>5.4</v>
       </c>
       <c r="M61" s="28"/>
       <c r="Q61" s="45"/>
@@ -6137,27 +6137,27 @@
       <c r="F62" s="62"/>
       <c r="G62" s="63"/>
       <c r="H62" s="62"/>
-      <c r="I62" s="72" t="s">
+      <c r="I62" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="J62" s="73"/>
-      <c r="K62" s="73"/>
-      <c r="L62" s="74">
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="69">
         <f>SUM(L10:L61)</f>
-        <v>79.136599999999973</v>
+        <v>55.999999999999993</v>
       </c>
       <c r="M62" s="63"/>
       <c r="Q62" s="45"/>
     </row>
     <row r="63" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I63" s="72" t="s">
+      <c r="I63" s="76" t="s">
         <v>260</v>
       </c>
-      <c r="J63" s="73"/>
-      <c r="K63" s="73"/>
-      <c r="L63" s="75">
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="70">
         <f>L62/2</f>
-        <v>39.568299999999986</v>
+        <v>27.999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -6200,11 +6200,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6242,7 +6242,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="66"/>
+      <c r="M3" s="74"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6261,7 +6261,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="46"/>
       <c r="L4" s="46"/>
-      <c r="M4" s="67"/>
+      <c r="M4" s="75"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6280,7 +6280,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="46"/>
       <c r="L5" s="46"/>
-      <c r="M5" s="67"/>
+      <c r="M5" s="75"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6295,7 +6295,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="46"/>
       <c r="L6" s="46"/>
-      <c r="M6" s="67"/>
+      <c r="M6" s="75"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6310,7 +6310,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="67"/>
+      <c r="M7" s="75"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6325,7 +6325,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="67"/>
+      <c r="M8" s="75"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6400,8 +6400,8 @@
         <f>J10*5</f>
         <v>20</v>
       </c>
-      <c r="L10" s="68">
-        <v>1.52</v>
+      <c r="L10" s="65">
+        <v>0.88</v>
       </c>
       <c r="M10" s="27"/>
     </row>
@@ -6439,8 +6439,8 @@
         <f t="shared" ref="K11" si="1">J11*5</f>
         <v>20</v>
       </c>
-      <c r="L11" s="69">
-        <v>2.0760000000000001</v>
+      <c r="L11" s="66">
+        <v>0.78</v>
       </c>
       <c r="M11" s="28"/>
     </row>
@@ -6478,8 +6478,8 @@
         <f>J12*5</f>
         <v>5</v>
       </c>
-      <c r="L12" s="68">
-        <v>1.3450000000000002</v>
+      <c r="L12" s="65">
+        <v>0.65</v>
       </c>
       <c r="M12" s="27"/>
     </row>
@@ -6517,8 +6517,8 @@
         <f t="shared" ref="K13" si="2">J13*5</f>
         <v>5</v>
       </c>
-      <c r="L13" s="69">
-        <v>1.22</v>
+      <c r="L13" s="66">
+        <v>0.7</v>
       </c>
       <c r="M13" s="28"/>
     </row>
@@ -6556,8 +6556,8 @@
         <f>J14*5</f>
         <v>5</v>
       </c>
-      <c r="L14" s="68">
-        <v>1.3540000000000001</v>
+      <c r="L14" s="65">
+        <v>0.69</v>
       </c>
       <c r="M14" s="27"/>
     </row>
@@ -6595,8 +6595,8 @@
         <f t="shared" ref="K15" si="3">J15*5</f>
         <v>10</v>
       </c>
-      <c r="L15" s="69">
-        <v>1.4780000000000002</v>
+      <c r="L15" s="66">
+        <v>4.7</v>
       </c>
       <c r="M15" s="28"/>
     </row>
@@ -6634,8 +6634,8 @@
         <f>J16*5</f>
         <v>5</v>
       </c>
-      <c r="L16" s="68">
-        <v>1.37</v>
+      <c r="L16" s="65">
+        <v>0.7</v>
       </c>
       <c r="M16" s="27"/>
     </row>
@@ -6673,8 +6673,8 @@
         <f t="shared" ref="K17" si="4">J17*5</f>
         <v>5</v>
       </c>
-      <c r="L17" s="69">
-        <v>1.38</v>
+      <c r="L17" s="66">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M17" s="28"/>
     </row>
@@ -6712,8 +6712,8 @@
         <f>J18*5</f>
         <v>5</v>
       </c>
-      <c r="L18" s="68">
-        <v>1.3</v>
+      <c r="L18" s="65">
+        <v>0.77</v>
       </c>
       <c r="M18" s="27"/>
     </row>
@@ -6751,8 +6751,8 @@
         <f t="shared" ref="K19" si="5">J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="69">
-        <v>5.4706999999999999</v>
+      <c r="L19" s="66">
+        <v>0.66</v>
       </c>
       <c r="M19" s="28"/>
     </row>
@@ -6790,8 +6790,8 @@
         <f>J20*5</f>
         <v>5</v>
       </c>
-      <c r="L20" s="68">
-        <v>1.5649999999999999</v>
+      <c r="L20" s="65">
+        <v>0.78</v>
       </c>
       <c r="M20" s="27"/>
     </row>
@@ -6829,8 +6829,8 @@
         <f t="shared" ref="K21" si="6">J21*5</f>
         <v>5</v>
       </c>
-      <c r="L21" s="69">
-        <v>2.8291999999999997</v>
+      <c r="L21" s="66">
+        <v>0.67500000000000004</v>
       </c>
       <c r="M21" s="28"/>
     </row>
@@ -6868,8 +6868,8 @@
         <f>J22*5</f>
         <v>5</v>
       </c>
-      <c r="L22" s="68">
-        <v>1.175</v>
+      <c r="L22" s="65">
+        <v>0.7</v>
       </c>
       <c r="M22" s="27"/>
     </row>
@@ -6907,8 +6907,8 @@
         <f t="shared" ref="K23" si="7">J23*5</f>
         <v>5</v>
       </c>
-      <c r="L23" s="69">
-        <v>1.6120000000000001</v>
+      <c r="L23" s="66">
+        <v>0.88</v>
       </c>
       <c r="M23" s="28"/>
     </row>
@@ -6946,8 +6946,8 @@
         <f>J24*5</f>
         <v>5</v>
       </c>
-      <c r="L24" s="68">
-        <v>1.756</v>
+      <c r="L24" s="65">
+        <v>0.8</v>
       </c>
       <c r="M24" s="27"/>
     </row>
@@ -6985,8 +6985,8 @@
         <f t="shared" ref="K25" si="8">J25*5</f>
         <v>5</v>
       </c>
-      <c r="L25" s="69">
-        <v>1.625</v>
+      <c r="L25" s="66">
+        <v>0.95</v>
       </c>
       <c r="M25" s="28"/>
     </row>
@@ -7024,8 +7024,8 @@
         <f>J26*5</f>
         <v>5</v>
       </c>
-      <c r="L26" s="68">
-        <v>1.9849999999999999</v>
+      <c r="L26" s="65">
+        <v>3.85</v>
       </c>
       <c r="M26" s="27"/>
     </row>
@@ -7063,7 +7063,7 @@
         <f t="shared" ref="K27" si="9">J27*5</f>
         <v>10</v>
       </c>
-      <c r="L27" s="69">
+      <c r="L27" s="66">
         <v>5.5070000000000006</v>
       </c>
       <c r="M27" s="28"/>
@@ -7102,8 +7102,8 @@
         <f>J28*5</f>
         <v>65</v>
       </c>
-      <c r="L28" s="68">
-        <v>2.7040000000000002</v>
+      <c r="L28" s="65">
+        <v>1.2</v>
       </c>
       <c r="M28" s="27"/>
     </row>
@@ -7141,8 +7141,8 @@
         <f t="shared" ref="K29" si="10">J29*5</f>
         <v>5</v>
       </c>
-      <c r="L29" s="69">
-        <v>1.675</v>
+      <c r="L29" s="66">
+        <v>0.76</v>
       </c>
       <c r="M29" s="28"/>
     </row>
@@ -7180,8 +7180,8 @@
         <f>J30*5</f>
         <v>20</v>
       </c>
-      <c r="L30" s="68">
-        <v>1.8199999999999998</v>
+      <c r="L30" s="65">
+        <v>1</v>
       </c>
       <c r="M30" s="27"/>
     </row>
@@ -7219,8 +7219,8 @@
         <f t="shared" ref="K31" si="11">J31*5</f>
         <v>10</v>
       </c>
-      <c r="L31" s="69">
-        <v>1.52</v>
+      <c r="L31" s="66">
+        <v>0.65</v>
       </c>
       <c r="M31" s="28"/>
     </row>
@@ -7258,8 +7258,8 @@
         <f>J32*5</f>
         <v>5</v>
       </c>
-      <c r="L32" s="68">
-        <v>1.488</v>
+      <c r="L32" s="65">
+        <v>0.75</v>
       </c>
       <c r="M32" s="27"/>
     </row>
@@ -7294,7 +7294,7 @@
         <f t="shared" ref="K33:K34" si="12">J33*5</f>
         <v>5</v>
       </c>
-      <c r="L33" s="68">
+      <c r="L33" s="65">
         <v>4.37</v>
       </c>
       <c r="M33" s="28"/>
@@ -7333,8 +7333,8 @@
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="L34" s="68">
-        <v>1.512</v>
+      <c r="L34" s="65">
+        <v>0.75</v>
       </c>
       <c r="M34" s="27"/>
     </row>
@@ -7372,8 +7372,8 @@
         <f>J35*5</f>
         <v>5</v>
       </c>
-      <c r="L35" s="68">
-        <v>1.464</v>
+      <c r="L35" s="65">
+        <v>0.66</v>
       </c>
       <c r="M35" s="28"/>
     </row>
@@ -7411,8 +7411,8 @@
         <f t="shared" ref="K36" si="13">J36*5</f>
         <v>10</v>
       </c>
-      <c r="L36" s="68">
-        <v>1.335</v>
+      <c r="L36" s="65">
+        <v>0.78</v>
       </c>
       <c r="M36" s="27"/>
     </row>
@@ -7450,8 +7450,8 @@
         <f>J37*5</f>
         <v>15</v>
       </c>
-      <c r="L37" s="68">
-        <v>1.7799999999999998</v>
+      <c r="L37" s="65">
+        <v>0.9</v>
       </c>
       <c r="M37" s="28"/>
     </row>
@@ -7489,8 +7489,8 @@
         <f t="shared" ref="K38" si="14">J38*5</f>
         <v>10</v>
       </c>
-      <c r="L38" s="68">
-        <v>1.4220000000000002</v>
+      <c r="L38" s="65">
+        <v>0.75</v>
       </c>
       <c r="M38" s="27"/>
     </row>
@@ -7528,8 +7528,8 @@
         <f>J39*5</f>
         <v>15</v>
       </c>
-      <c r="L39" s="68">
-        <v>1.492</v>
+      <c r="L39" s="65">
+        <v>0.85</v>
       </c>
       <c r="M39" s="28"/>
     </row>
@@ -7567,8 +7567,8 @@
         <f t="shared" ref="K40" si="15">J40*5</f>
         <v>10</v>
       </c>
-      <c r="L40" s="68">
-        <v>1.33</v>
+      <c r="L40" s="65">
+        <v>0.77</v>
       </c>
       <c r="M40" s="27"/>
     </row>
@@ -7606,8 +7606,8 @@
         <f>J41*5</f>
         <v>15</v>
       </c>
-      <c r="L41" s="68">
-        <v>1.516</v>
+      <c r="L41" s="65">
+        <v>0.98</v>
       </c>
       <c r="M41" s="28"/>
     </row>
@@ -7643,8 +7643,8 @@
         <f t="shared" ref="K42" si="16">J42*5</f>
         <v>15</v>
       </c>
-      <c r="L42" s="68">
-        <v>0.99</v>
+      <c r="L42" s="65">
+        <v>0.76300000000000001</v>
       </c>
       <c r="M42" s="27"/>
     </row>
@@ -7682,8 +7682,8 @@
         <f>J43*5</f>
         <v>10</v>
       </c>
-      <c r="L43" s="68">
-        <v>1.04</v>
+      <c r="L43" s="65">
+        <v>0.8</v>
       </c>
       <c r="M43" s="28"/>
     </row>
@@ -7721,8 +7721,8 @@
         <f t="shared" ref="K44" si="17">J44*5</f>
         <v>15</v>
       </c>
-      <c r="L44" s="68">
-        <v>1.464</v>
+      <c r="L44" s="65">
+        <v>0.9</v>
       </c>
       <c r="M44" s="27"/>
     </row>
@@ -7760,8 +7760,8 @@
         <f>J45*5</f>
         <v>10</v>
       </c>
-      <c r="L45" s="68">
-        <v>1.4180000000000001</v>
+      <c r="L45" s="65">
+        <v>0.7</v>
       </c>
       <c r="M45" s="28"/>
     </row>
@@ -7799,8 +7799,8 @@
         <f t="shared" ref="K46" si="18">J46*5</f>
         <v>15</v>
       </c>
-      <c r="L46" s="68">
-        <v>1.524</v>
+      <c r="L46" s="65">
+        <v>0.81</v>
       </c>
       <c r="M46" s="27"/>
     </row>
@@ -7838,8 +7838,8 @@
         <f>J47*5</f>
         <v>10</v>
       </c>
-      <c r="L47" s="68">
-        <v>1.476</v>
+      <c r="L47" s="65">
+        <v>0.75</v>
       </c>
       <c r="M47" s="28"/>
     </row>
@@ -7877,8 +7877,8 @@
         <f t="shared" ref="K48" si="19">J48*5</f>
         <v>10</v>
       </c>
-      <c r="L48" s="68">
-        <v>1.5680000000000001</v>
+      <c r="L48" s="65">
+        <v>0.88</v>
       </c>
       <c r="M48" s="27"/>
     </row>
@@ -7916,8 +7916,8 @@
         <f>J49*5</f>
         <v>15</v>
       </c>
-      <c r="L49" s="68">
-        <v>1.4359999999999999</v>
+      <c r="L49" s="65">
+        <v>0.96</v>
       </c>
       <c r="M49" s="28"/>
     </row>
@@ -7955,8 +7955,8 @@
         <f t="shared" ref="K50" si="20">J50*5</f>
         <v>5</v>
       </c>
-      <c r="L50" s="68">
-        <v>1.508</v>
+      <c r="L50" s="65">
+        <v>0.48</v>
       </c>
       <c r="M50" s="27"/>
     </row>
@@ -7994,8 +7994,8 @@
         <f>J51*5</f>
         <v>5</v>
       </c>
-      <c r="L51" s="68">
-        <v>1.1100000000000001</v>
+      <c r="L51" s="65">
+        <v>0.55000000000000004</v>
       </c>
       <c r="M51" s="28"/>
     </row>
@@ -8033,8 +8033,8 @@
         <f t="shared" ref="K52" si="21">J52*5</f>
         <v>5</v>
       </c>
-      <c r="L52" s="68">
-        <v>1.6920000000000002</v>
+      <c r="L52" s="65">
+        <v>0.88</v>
       </c>
       <c r="M52" s="27"/>
     </row>
@@ -8072,8 +8072,8 @@
         <f>J53*5</f>
         <v>5</v>
       </c>
-      <c r="L53" s="68">
-        <v>1.3540000000000001</v>
+      <c r="L53" s="65">
+        <v>0.42</v>
       </c>
       <c r="M53" s="28"/>
     </row>
@@ -8111,8 +8111,8 @@
         <f t="shared" ref="K54" si="22">J54*5</f>
         <v>5</v>
       </c>
-      <c r="L54" s="68">
-        <v>1.544</v>
+      <c r="L54" s="65">
+        <v>0.53</v>
       </c>
       <c r="M54" s="27"/>
       <c r="P54"/>
@@ -8151,8 +8151,8 @@
         <f>J55*5</f>
         <v>5</v>
       </c>
-      <c r="L55" s="68">
-        <v>1.4239999999999999</v>
+      <c r="L55" s="65">
+        <v>0.68</v>
       </c>
       <c r="M55" s="28"/>
     </row>
@@ -8190,8 +8190,8 @@
         <f t="shared" ref="K56:K57" si="23">J56*5</f>
         <v>5</v>
       </c>
-      <c r="L56" s="68">
-        <v>1.3940000000000001</v>
+      <c r="L56" s="65">
+        <v>0.74</v>
       </c>
       <c r="M56" s="27"/>
     </row>
@@ -8229,7 +8229,7 @@
         <f t="shared" si="23"/>
         <v>5</v>
       </c>
-      <c r="L57" s="69">
+      <c r="L57" s="66">
         <v>2.36</v>
       </c>
       <c r="M57" s="28"/>
@@ -8268,8 +8268,8 @@
         <f>J58*5</f>
         <v>10</v>
       </c>
-      <c r="L58" s="68">
-        <v>1.4279999999999999</v>
+      <c r="L58" s="65">
+        <v>0.88</v>
       </c>
       <c r="M58" s="27"/>
     </row>
@@ -8307,7 +8307,7 @@
         <f t="shared" ref="K59" si="24">J59*5</f>
         <v>10</v>
       </c>
-      <c r="L59" s="70" t="s">
+      <c r="L59" s="67" t="s">
         <v>236</v>
       </c>
       <c r="M59" s="28"/>
@@ -8346,8 +8346,8 @@
         <f>J60*5</f>
         <v>45</v>
       </c>
-      <c r="L60" s="68">
-        <v>22.756200000000003</v>
+      <c r="L60" s="65">
+        <v>29.5</v>
       </c>
       <c r="M60" s="28"/>
       <c r="R60" s="45"/>
@@ -8386,8 +8386,8 @@
         <f t="shared" ref="K61" si="25">J61*5</f>
         <v>15</v>
       </c>
-      <c r="L61" s="71">
-        <v>3.198</v>
+      <c r="L61" s="68">
+        <v>10.199999999999999</v>
       </c>
       <c r="M61" s="51"/>
       <c r="R61" s="45"/>
@@ -8400,27 +8400,27 @@
       <c r="F62" s="56"/>
       <c r="G62" s="57"/>
       <c r="H62" s="56"/>
-      <c r="I62" s="72" t="s">
+      <c r="I62" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="J62" s="73"/>
-      <c r="K62" s="73"/>
-      <c r="L62" s="74">
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="69">
         <f>SUM(L10:L61)</f>
-        <v>112.68010000000001</v>
+        <v>94.185000000000016</v>
       </c>
       <c r="M62" s="64"/>
       <c r="R62" s="45"/>
     </row>
     <row r="63" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I63" s="72" t="s">
+      <c r="I63" s="76" t="s">
         <v>260</v>
       </c>
-      <c r="J63" s="73"/>
-      <c r="K63" s="73"/>
-      <c r="L63" s="75">
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="70">
         <f>L62/5</f>
-        <v>22.536020000000001</v>
+        <v>18.837000000000003</v>
       </c>
       <c r="R63" s="45"/>
     </row>

--- a/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/Client-BOM-Xponent-tech.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="263">
   <si>
     <t>Component list</t>
   </si>
@@ -3185,7 +3185,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="40"/>
+      <c r="C42" s="42" t="s">
+        <v>10</v>
+      </c>
       <c r="D42" s="48" t="s">
         <v>44</v>
       </c>
@@ -5355,7 +5357,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="40"/>
+      <c r="C42" s="42" t="s">
+        <v>10</v>
+      </c>
       <c r="D42" s="48" t="s">
         <v>44</v>
       </c>
@@ -7617,7 +7621,9 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="40"/>
+      <c r="C42" s="42" t="s">
+        <v>10</v>
+      </c>
       <c r="D42" s="48" t="s">
         <v>44</v>
       </c>
